--- a/recipes/onion-garlic-free-indian/focus-states/17-pan-india/excel/pan-india-recipes.xlsx
+++ b/recipes/onion-garlic-free-indian/focus-states/17-pan-india/excel/pan-india-recipes.xlsx
@@ -104,7 +104,7 @@
       <name val="Calibri"/>
       <b val="1"/>
       <color rgb="009A3412"/>
-      <sz val="16"/>
+      <sz val="12"/>
     </font>
   </fonts>
   <fills count="19">
@@ -259,7 +259,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="49">
+  <cellXfs count="52">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
@@ -357,6 +357,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="18" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1464,7 +1467,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D16"/>
+  <dimension ref="A1:D29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1476,7 +1479,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RECIPE CARD  ·  Aloo gobi (national dry, no onion)</t>
+          <t>Parslia Kitchen OS · RECIPE CARD · Aloo gobi (national dry, no onion)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1486,7 +1489,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Pan-India kitchen  ·  Side  ·  Dishes cooked in homes all over India</t>
+          <t>Pure Prasad · No onion · No garlic · No eggs · No meat · No fish  ·  Pan-India  ·  Side</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -1506,44 +1509,44 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="38" t="inlineStr">
         <is>
-          <t>Serves</t>
+          <t>YIELD</t>
         </is>
       </c>
       <c r="B5" s="38" t="inlineStr">
         <is>
-          <t>Prep</t>
+          <t>PORTION</t>
         </is>
       </c>
       <c r="C5" s="38" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>SERVICE</t>
         </is>
       </c>
       <c r="D5" s="38" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>TIME</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="39" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 portions</t>
         </is>
       </c>
       <c r="B6" s="39" t="inlineStr">
         <is>
-          <t>15 min</t>
+          <t>1 portion</t>
         </is>
       </c>
       <c r="C6" s="39" t="inlineStr">
         <is>
-          <t>25 min</t>
+          <t>Hot</t>
         </is>
       </c>
       <c r="D6" s="39" t="inlineStr">
         <is>
-          <t>40 min</t>
+          <t>Prep 15 min · Cook 25 min</t>
         </is>
       </c>
     </row>
@@ -1619,29 +1622,169 @@
       <c r="C15" s="45" t="n"/>
       <c r="D15" s="45" t="n"/>
     </row>
-    <row r="16" ht="36" customHeight="1">
+    <row r="16" ht="42" customHeight="1">
       <c r="A16" s="46" t="n">
         <v>1</v>
       </c>
       <c r="B16" s="47" t="inlineStr">
         <is>
-          <t>Cover-cook dry.</t>
+          <t>Mise en place. Even florets and potato cubes. Steel kadhai — never aluminium.</t>
         </is>
       </c>
       <c r="C16" s="48" t="n"/>
       <c r="D16" s="48" t="n"/>
     </row>
+    <row r="17" ht="42" customHeight="1">
+      <c r="A17" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="B17" s="30" t="inlineStr">
+        <is>
+          <t>Bloom cumin and hing in ghee. Add vegetables, turmeric, chilli, coriander and salt. Cover-cook 12–15 minutes, stirring.</t>
+        </is>
+      </c>
+      <c r="C17" s="31" t="n"/>
+      <c r="D17" s="31" t="n"/>
+    </row>
+    <row r="18" ht="36" customHeight="1">
+      <c r="A18" s="46" t="n">
+        <v>3</v>
+      </c>
+      <c r="B18" s="47" t="inlineStr">
+        <is>
+          <t>Uncover and dry the masala 2–3 minutes so it clings.</t>
+        </is>
+      </c>
+      <c r="C18" s="48" t="n"/>
+      <c r="D18" s="48" t="n"/>
+    </row>
+    <row r="19" ht="36" customHeight="1">
+      <c r="A19" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="B19" s="30" t="inlineStr">
+        <is>
+          <t>Doneness: tender with dry spice coat, not mush. Serve hot as a side.</t>
+        </is>
+      </c>
+      <c r="C19" s="31" t="n"/>
+      <c r="D19" s="31" t="n"/>
+    </row>
+    <row r="20" ht="36" customHeight="1">
+      <c r="A20" s="46" t="n">
+        <v>5</v>
+      </c>
+      <c r="B20" s="47" t="inlineStr">
+        <is>
+          <t>Hold covered 20 minutes.</t>
+        </is>
+      </c>
+      <c r="C20" s="48" t="n"/>
+      <c r="D20" s="48" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="21" t="inlineStr">
+        <is>
+          <t>Nutrition per portion</t>
+        </is>
+      </c>
+      <c r="B22" s="22" t="n"/>
+      <c r="C22" s="22" t="n"/>
+      <c r="D22" s="22" t="n"/>
+    </row>
+    <row r="23" ht="36" customHeight="1">
+      <c r="A23" s="12" t="inlineStr">
+        <is>
+          <t>kcal 0  ·  Protein 0 g  ·  Carbs 0 g  ·  Fat 0 g  ·  Fibre 0 g. Nutrition is a kitchen estimate from typical produce values, not a laboratory analysis.</t>
+        </is>
+      </c>
+      <c r="B23" s="49" t="n"/>
+      <c r="C23" s="49" t="n"/>
+      <c r="D23" s="49" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="24" t="inlineStr">
+        <is>
+          <t>Allergens</t>
+        </is>
+      </c>
+      <c r="B24" s="6" t="n"/>
+      <c r="C24" s="6" t="n"/>
+      <c r="D24" s="6" t="n"/>
+    </row>
+    <row r="25" ht="48" customHeight="1">
+      <c r="A25" s="25" t="inlineStr">
+        <is>
+          <t>Gluten (wheat) · Milk · Always verify labels; this card is a kitchen estimate, not a lab certificate.</t>
+        </is>
+      </c>
+      <c r="B25" s="26" t="n"/>
+      <c r="C25" s="26" t="n"/>
+      <c r="D25" s="26" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="24" t="inlineStr">
+        <is>
+          <t>Chef notes</t>
+        </is>
+      </c>
+      <c r="B26" s="6" t="n"/>
+      <c r="C26" s="6" t="n"/>
+      <c r="D26" s="6" t="n"/>
+    </row>
+    <row r="27" ht="72" customHeight="1">
+      <c r="A27" s="25" t="inlineStr">
+        <is>
+          <t>For Aloo gobi (national dry, no onion): keep the mix slightly drier than you think; wet mixes split or go greasy. Bloom hing in hot fat 20–30 seconds; raw hing tastes medicinal. Commercial hing is often cut with wheat flour — use a gluten-free hing if you must mark Gluten Free. Never cook tomato, tamarind, lemon, yogurt or milk in aluminium; use stainless steel, iron, clay or glass. Spice blends: read the packet. Many garam masalas hide onion or garlic powder.</t>
+        </is>
+      </c>
+      <c r="B27" s="26" t="n"/>
+      <c r="C27" s="26" t="n"/>
+      <c r="D27" s="26" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="50" t="inlineStr">
+        <is>
+          <t>Service notes</t>
+        </is>
+      </c>
+      <c r="B28" s="51" t="n"/>
+      <c r="C28" s="51" t="n"/>
+      <c r="D28" s="51" t="n"/>
+    </row>
+    <row r="29" ht="64" customHeight="1">
+      <c r="A29" s="12" t="inlineStr">
+        <is>
+          <t>Serve family-style in a steel bowl. Keep a lid on at the pass so it does not skin. Service temperature: Hot. Allergen label for this dish: Gluten (wheat); Milk; Always verify labels; this card is a kitchen estimate, not a lab certificate. State clearly: vegetarian, no onion, no garlic, no eggs, no meat, no fish. Nutrition on this card is an estimate for 1 portion of 4.</t>
+        </is>
+      </c>
+      <c r="B29" s="49" t="n"/>
+      <c r="C29" s="49" t="n"/>
+      <c r="D29" s="49" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="22">
+    <mergeCell ref="A23:D23"/>
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="A22:D22"/>
+    <mergeCell ref="B17:D17"/>
+    <mergeCell ref="A29:D29"/>
+    <mergeCell ref="A28:D28"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="B19:D19"/>
+    <mergeCell ref="A24:D24"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B15:D15"/>
+    <mergeCell ref="B20:D20"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="C12:D12"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="A25:D25"/>
+    <mergeCell ref="B16:D16"/>
+    <mergeCell ref="A27:D27"/>
     <mergeCell ref="A3:D3"/>
+    <mergeCell ref="A26:D26"/>
+    <mergeCell ref="B18:D18"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="B15:D15"/>
-    <mergeCell ref="B16:D16"/>
     <mergeCell ref="A14:D14"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1656,7 +1799,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D16"/>
+  <dimension ref="A1:D29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1668,7 +1811,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RECIPE CARD  ·  Bhindi masala (no onion garlic)</t>
+          <t>Parslia Kitchen OS · RECIPE CARD · Bhindi masala (no onion garlic)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1678,7 +1821,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Pan-India kitchen  ·  Side  ·  Dishes cooked in homes all over India</t>
+          <t>Pure Prasad · No onion · No garlic · No eggs · No meat · No fish  ·  Pan-India  ·  Side</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -1698,44 +1841,44 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="38" t="inlineStr">
         <is>
-          <t>Serves</t>
+          <t>YIELD</t>
         </is>
       </c>
       <c r="B5" s="38" t="inlineStr">
         <is>
-          <t>Prep</t>
+          <t>PORTION</t>
         </is>
       </c>
       <c r="C5" s="38" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>SERVICE</t>
         </is>
       </c>
       <c r="D5" s="38" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>TIME</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="39" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 portions</t>
         </is>
       </c>
       <c r="B6" s="39" t="inlineStr">
         <is>
-          <t>15 min</t>
+          <t>1 portion</t>
         </is>
       </c>
       <c r="C6" s="39" t="inlineStr">
         <is>
-          <t>20 min</t>
+          <t>Hot</t>
         </is>
       </c>
       <c r="D6" s="39" t="inlineStr">
         <is>
-          <t>35 min</t>
+          <t>Prep 15 min · Cook 20 min</t>
         </is>
       </c>
     </row>
@@ -1811,29 +1954,169 @@
       <c r="C15" s="45" t="n"/>
       <c r="D15" s="45" t="n"/>
     </row>
-    <row r="16" ht="36" customHeight="1">
+    <row r="16" ht="42" customHeight="1">
       <c r="A16" s="46" t="n">
         <v>1</v>
       </c>
       <c r="B16" s="47" t="inlineStr">
         <is>
-          <t>Fry bhindi first to reduce slime. Mix masala.</t>
+          <t>Mise en place. Wipe 500 g okra dry — water makes slime. Cut 3 cm pieces. Steel kadhai — never aluminium.</t>
         </is>
       </c>
       <c r="C16" s="48" t="n"/>
       <c r="D16" s="48" t="n"/>
     </row>
+    <row r="17" ht="42" customHeight="1">
+      <c r="A17" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="B17" s="30" t="inlineStr">
+        <is>
+          <t>Fry okra in oil on medium-high 6–8 minutes until the slime cooks off and edges colour. Lift out.</t>
+        </is>
+      </c>
+      <c r="C17" s="31" t="n"/>
+      <c r="D17" s="31" t="n"/>
+    </row>
+    <row r="18" ht="42" customHeight="1">
+      <c r="A18" s="46" t="n">
+        <v>3</v>
+      </c>
+      <c r="B18" s="47" t="inlineStr">
+        <is>
+          <t>In the same pan bloom cumin and hing. Cook tomato, chilli, coriander, amchur and salt 4 minutes. Return okra. Toss 3 minutes.</t>
+        </is>
+      </c>
+      <c r="C18" s="48" t="n"/>
+      <c r="D18" s="48" t="n"/>
+    </row>
+    <row r="19" ht="36" customHeight="1">
+      <c r="A19" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="B19" s="30" t="inlineStr">
+        <is>
+          <t>Doneness: okra tender not mushy, masala dry on the pieces. Serve hot.</t>
+        </is>
+      </c>
+      <c r="C19" s="31" t="n"/>
+      <c r="D19" s="31" t="n"/>
+    </row>
+    <row r="20" ht="36" customHeight="1">
+      <c r="A20" s="46" t="n">
+        <v>5</v>
+      </c>
+      <c r="B20" s="47" t="inlineStr">
+        <is>
+          <t>Hold uncovered a few minutes so steam does not return the slime.</t>
+        </is>
+      </c>
+      <c r="C20" s="48" t="n"/>
+      <c r="D20" s="48" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="21" t="inlineStr">
+        <is>
+          <t>Nutrition per portion</t>
+        </is>
+      </c>
+      <c r="B22" s="22" t="n"/>
+      <c r="C22" s="22" t="n"/>
+      <c r="D22" s="22" t="n"/>
+    </row>
+    <row r="23" ht="36" customHeight="1">
+      <c r="A23" s="12" t="inlineStr">
+        <is>
+          <t>kcal 0  ·  Protein 0 g  ·  Carbs 0 g  ·  Fat 0 g  ·  Fibre 0 g. Nutrition is a kitchen estimate from typical produce values, not a laboratory analysis.</t>
+        </is>
+      </c>
+      <c r="B23" s="49" t="n"/>
+      <c r="C23" s="49" t="n"/>
+      <c r="D23" s="49" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="24" t="inlineStr">
+        <is>
+          <t>Allergens</t>
+        </is>
+      </c>
+      <c r="B24" s="6" t="n"/>
+      <c r="C24" s="6" t="n"/>
+      <c r="D24" s="6" t="n"/>
+    </row>
+    <row r="25" ht="48" customHeight="1">
+      <c r="A25" s="25" t="inlineStr">
+        <is>
+          <t>Gluten (wheat) · Always verify labels; this card is a kitchen estimate, not a lab certificate.</t>
+        </is>
+      </c>
+      <c r="B25" s="26" t="n"/>
+      <c r="C25" s="26" t="n"/>
+      <c r="D25" s="26" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="24" t="inlineStr">
+        <is>
+          <t>Chef notes</t>
+        </is>
+      </c>
+      <c r="B26" s="6" t="n"/>
+      <c r="C26" s="6" t="n"/>
+      <c r="D26" s="6" t="n"/>
+    </row>
+    <row r="27" ht="72" customHeight="1">
+      <c r="A27" s="25" t="inlineStr">
+        <is>
+          <t>For Bhindi masala (no onion garlic): keep the mix slightly drier than you think; wet mixes split or go greasy. Bloom hing in hot fat 20–30 seconds; raw hing tastes medicinal. Commercial hing is often cut with wheat flour — use a gluten-free hing if you must mark Gluten Free. Never cook tomato, tamarind, lemon, yogurt or milk in aluminium; use stainless steel, iron, clay or glass. Spice blends: read the packet. Many garam masalas hide onion or garlic powder.</t>
+        </is>
+      </c>
+      <c r="B27" s="26" t="n"/>
+      <c r="C27" s="26" t="n"/>
+      <c r="D27" s="26" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="50" t="inlineStr">
+        <is>
+          <t>Service notes</t>
+        </is>
+      </c>
+      <c r="B28" s="51" t="n"/>
+      <c r="C28" s="51" t="n"/>
+      <c r="D28" s="51" t="n"/>
+    </row>
+    <row r="29" ht="64" customHeight="1">
+      <c r="A29" s="12" t="inlineStr">
+        <is>
+          <t>Serve family-style in a steel bowl. Keep a lid on at the pass so it does not skin. Service temperature: Hot. Allergen label for this dish: Gluten (wheat); Always verify labels; this card is a kitchen estimate, not a lab certificate. State clearly: vegetarian, no onion, no garlic, no eggs, no meat, no fish. Nutrition on this card is an estimate for 1 portion of 4.</t>
+        </is>
+      </c>
+      <c r="B29" s="49" t="n"/>
+      <c r="C29" s="49" t="n"/>
+      <c r="D29" s="49" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="22">
+    <mergeCell ref="A23:D23"/>
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="A22:D22"/>
+    <mergeCell ref="B17:D17"/>
+    <mergeCell ref="A29:D29"/>
+    <mergeCell ref="A28:D28"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="B19:D19"/>
+    <mergeCell ref="A24:D24"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B15:D15"/>
+    <mergeCell ref="B20:D20"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="C12:D12"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="A25:D25"/>
+    <mergeCell ref="B16:D16"/>
+    <mergeCell ref="A27:D27"/>
     <mergeCell ref="A3:D3"/>
+    <mergeCell ref="A26:D26"/>
+    <mergeCell ref="B18:D18"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="B15:D15"/>
-    <mergeCell ref="B16:D16"/>
     <mergeCell ref="A14:D14"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1848,7 +2131,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D16"/>
+  <dimension ref="A1:D29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1860,7 +2143,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RECIPE CARD  ·  Jeera aloo (no onion)</t>
+          <t>Parslia Kitchen OS · RECIPE CARD · Jeera aloo (no onion)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1870,7 +2153,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Pan-India kitchen  ·  Side  ·  Dishes cooked in homes all over India</t>
+          <t>Pure Prasad · No onion · No garlic · No eggs · No meat · No fish  ·  Pan-India  ·  Side</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -1890,44 +2173,44 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="38" t="inlineStr">
         <is>
-          <t>Serves</t>
+          <t>YIELD</t>
         </is>
       </c>
       <c r="B5" s="38" t="inlineStr">
         <is>
-          <t>Prep</t>
+          <t>PORTION</t>
         </is>
       </c>
       <c r="C5" s="38" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>SERVICE</t>
         </is>
       </c>
       <c r="D5" s="38" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>TIME</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="39" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 portions</t>
         </is>
       </c>
       <c r="B6" s="39" t="inlineStr">
         <is>
-          <t>10 min</t>
+          <t>1 portion</t>
         </is>
       </c>
       <c r="C6" s="39" t="inlineStr">
         <is>
-          <t>15 min</t>
+          <t>Hot</t>
         </is>
       </c>
       <c r="D6" s="39" t="inlineStr">
         <is>
-          <t>25 min</t>
+          <t>Prep 10 min · Cook 15 min</t>
         </is>
       </c>
     </row>
@@ -2003,29 +2286,169 @@
       <c r="C15" s="45" t="n"/>
       <c r="D15" s="45" t="n"/>
     </row>
-    <row r="16" ht="36" customHeight="1">
+    <row r="16" ht="42" customHeight="1">
       <c r="A16" s="46" t="n">
         <v>1</v>
       </c>
       <c r="B16" s="47" t="inlineStr">
         <is>
-          <t>Temper. Toss potatoes.</t>
+          <t>Mise en place. Boil 4 potatoes until just tender. Cool slightly. Cube. Steel kadhai — never aluminium.</t>
         </is>
       </c>
       <c r="C16" s="48" t="n"/>
       <c r="D16" s="48" t="n"/>
     </row>
+    <row r="17" ht="42" customHeight="1">
+      <c r="A17" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="B17" s="30" t="inlineStr">
+        <is>
+          <t>Heat ghee. Bloom cumin and hing until the cumin darkens a shade, 20–30 seconds. Add chilli.</t>
+        </is>
+      </c>
+      <c r="C17" s="31" t="n"/>
+      <c r="D17" s="31" t="n"/>
+    </row>
+    <row r="18" ht="42" customHeight="1">
+      <c r="A18" s="46" t="n">
+        <v>3</v>
+      </c>
+      <c r="B18" s="47" t="inlineStr">
+        <is>
+          <t>Toss potatoes with amchur, coriander and salt 3–4 minutes until edges take colour.</t>
+        </is>
+      </c>
+      <c r="C18" s="48" t="n"/>
+      <c r="D18" s="48" t="n"/>
+    </row>
+    <row r="19" ht="36" customHeight="1">
+      <c r="A19" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="B19" s="30" t="inlineStr">
+        <is>
+          <t>Doneness: potatoes hot, cumin fragrant, dry. Serve immediately.</t>
+        </is>
+      </c>
+      <c r="C19" s="31" t="n"/>
+      <c r="D19" s="31" t="n"/>
+    </row>
+    <row r="20" ht="36" customHeight="1">
+      <c r="A20" s="46" t="n">
+        <v>5</v>
+      </c>
+      <c r="B20" s="47" t="inlineStr">
+        <is>
+          <t>Hold 15 minutes covered. Do not add water.</t>
+        </is>
+      </c>
+      <c r="C20" s="48" t="n"/>
+      <c r="D20" s="48" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="21" t="inlineStr">
+        <is>
+          <t>Nutrition per portion</t>
+        </is>
+      </c>
+      <c r="B22" s="22" t="n"/>
+      <c r="C22" s="22" t="n"/>
+      <c r="D22" s="22" t="n"/>
+    </row>
+    <row r="23" ht="36" customHeight="1">
+      <c r="A23" s="12" t="inlineStr">
+        <is>
+          <t>kcal 0  ·  Protein 0 g  ·  Carbs 0 g  ·  Fat 0 g  ·  Fibre 0 g. Nutrition is a kitchen estimate from typical produce values, not a laboratory analysis.</t>
+        </is>
+      </c>
+      <c r="B23" s="49" t="n"/>
+      <c r="C23" s="49" t="n"/>
+      <c r="D23" s="49" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="24" t="inlineStr">
+        <is>
+          <t>Allergens</t>
+        </is>
+      </c>
+      <c r="B24" s="6" t="n"/>
+      <c r="C24" s="6" t="n"/>
+      <c r="D24" s="6" t="n"/>
+    </row>
+    <row r="25" ht="48" customHeight="1">
+      <c r="A25" s="25" t="inlineStr">
+        <is>
+          <t>Gluten (wheat) · Milk · Always verify labels; this card is a kitchen estimate, not a lab certificate.</t>
+        </is>
+      </c>
+      <c r="B25" s="26" t="n"/>
+      <c r="C25" s="26" t="n"/>
+      <c r="D25" s="26" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="24" t="inlineStr">
+        <is>
+          <t>Chef notes</t>
+        </is>
+      </c>
+      <c r="B26" s="6" t="n"/>
+      <c r="C26" s="6" t="n"/>
+      <c r="D26" s="6" t="n"/>
+    </row>
+    <row r="27" ht="72" customHeight="1">
+      <c r="A27" s="25" t="inlineStr">
+        <is>
+          <t>For Jeera aloo (no onion): keep the mix slightly drier than you think; wet mixes split or go greasy. Bloom hing in hot fat 20–30 seconds; raw hing tastes medicinal. Commercial hing is often cut with wheat flour — use a gluten-free hing if you must mark Gluten Free. Never cook tomato, tamarind, lemon, yogurt or milk in aluminium; use stainless steel, iron, clay or glass. Spice blends: read the packet. Many garam masalas hide onion or garlic powder.</t>
+        </is>
+      </c>
+      <c r="B27" s="26" t="n"/>
+      <c r="C27" s="26" t="n"/>
+      <c r="D27" s="26" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="50" t="inlineStr">
+        <is>
+          <t>Service notes</t>
+        </is>
+      </c>
+      <c r="B28" s="51" t="n"/>
+      <c r="C28" s="51" t="n"/>
+      <c r="D28" s="51" t="n"/>
+    </row>
+    <row r="29" ht="64" customHeight="1">
+      <c r="A29" s="12" t="inlineStr">
+        <is>
+          <t>Serve family-style in a steel bowl. Keep a lid on at the pass so it does not skin. Service temperature: Hot. Allergen label for this dish: Gluten (wheat); Milk; Always verify labels; this card is a kitchen estimate, not a lab certificate. State clearly: vegetarian, no onion, no garlic, no eggs, no meat, no fish. Nutrition on this card is an estimate for 1 portion of 4.</t>
+        </is>
+      </c>
+      <c r="B29" s="49" t="n"/>
+      <c r="C29" s="49" t="n"/>
+      <c r="D29" s="49" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="22">
+    <mergeCell ref="A23:D23"/>
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="A22:D22"/>
+    <mergeCell ref="B17:D17"/>
+    <mergeCell ref="A29:D29"/>
+    <mergeCell ref="A28:D28"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="B19:D19"/>
+    <mergeCell ref="A24:D24"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B15:D15"/>
+    <mergeCell ref="B20:D20"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="C12:D12"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="A25:D25"/>
+    <mergeCell ref="B16:D16"/>
+    <mergeCell ref="A27:D27"/>
     <mergeCell ref="A3:D3"/>
+    <mergeCell ref="A26:D26"/>
+    <mergeCell ref="B18:D18"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="B15:D15"/>
-    <mergeCell ref="B16:D16"/>
     <mergeCell ref="A14:D14"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2040,7 +2463,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D19"/>
+  <dimension ref="A1:D33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2052,7 +2475,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RECIPE CARD  ·  Phulka / roti (national)</t>
+          <t>Parslia Kitchen OS · RECIPE CARD · Phulka / roti (national)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2062,7 +2485,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Pan-India kitchen  ·  Bread  ·  Dishes cooked in homes all over India</t>
+          <t>Pure Prasad · No onion · No garlic · No eggs · No meat · No fish  ·  Pan-India  ·  Bread</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -2082,44 +2505,44 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="38" t="inlineStr">
         <is>
-          <t>Serves</t>
+          <t>YIELD</t>
         </is>
       </c>
       <c r="B5" s="38" t="inlineStr">
         <is>
-          <t>Prep</t>
+          <t>PORTION</t>
         </is>
       </c>
       <c r="C5" s="38" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>SERVICE</t>
         </is>
       </c>
       <c r="D5" s="38" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>TIME</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="39" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 portions</t>
         </is>
       </c>
       <c r="B6" s="39" t="inlineStr">
         <is>
-          <t>15 min</t>
+          <t>1 portion</t>
         </is>
       </c>
       <c r="C6" s="39" t="inlineStr">
         <is>
-          <t>20 min</t>
+          <t>Hot</t>
         </is>
       </c>
       <c r="D6" s="39" t="inlineStr">
         <is>
-          <t>35 min</t>
+          <t>Prep 15 min · Cook 20 min</t>
         </is>
       </c>
     </row>
@@ -2249,33 +2672,186 @@
       <c r="C18" s="45" t="n"/>
       <c r="D18" s="45" t="n"/>
     </row>
-    <row r="19" ht="36" customHeight="1">
+    <row r="19" ht="42" customHeight="1">
       <c r="A19" s="46" t="n">
         <v>1</v>
       </c>
       <c r="B19" s="47" t="inlineStr">
         <is>
-          <t>Roll. Tawa. Puff. Every Indian table.</t>
+          <t>Mise en place. Mix atta and water to a soft dough. Rest 10–15 minutes. Cast-iron tawa — not aluminium.</t>
         </is>
       </c>
       <c r="C19" s="48" t="n"/>
       <c r="D19" s="48" t="n"/>
     </row>
+    <row r="20" ht="36" customHeight="1">
+      <c r="A20" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="B20" s="30" t="inlineStr">
+        <is>
+          <t>Divide. Roll 2 mm thick, even, round. Dust lightly.</t>
+        </is>
+      </c>
+      <c r="C20" s="31" t="n"/>
+      <c r="D20" s="31" t="n"/>
+    </row>
+    <row r="21" ht="42" customHeight="1">
+      <c r="A21" s="46" t="n">
+        <v>3</v>
+      </c>
+      <c r="B21" s="47" t="inlineStr">
+        <is>
+          <t>Cook first side 20 seconds until bubbles. Flip. Cook until brown spots. Flip onto the flame or press to puff.</t>
+        </is>
+      </c>
+      <c r="C21" s="48" t="n"/>
+      <c r="D21" s="48" t="n"/>
+    </row>
+    <row r="22" ht="36" customHeight="1">
+      <c r="A22" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="B22" s="30" t="inlineStr">
+        <is>
+          <t>Optional ghee. Stack in a cloth.</t>
+        </is>
+      </c>
+      <c r="C22" s="31" t="n"/>
+      <c r="D22" s="31" t="n"/>
+    </row>
+    <row r="23" ht="36" customHeight="1">
+      <c r="A23" s="46" t="n">
+        <v>5</v>
+      </c>
+      <c r="B23" s="47" t="inlineStr">
+        <is>
+          <t>Doneness: puffed or fully cooked, no raw patches. Serve hot.</t>
+        </is>
+      </c>
+      <c r="C23" s="48" t="n"/>
+      <c r="D23" s="48" t="n"/>
+    </row>
+    <row r="24" ht="36" customHeight="1">
+      <c r="A24" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="B24" s="30" t="inlineStr">
+        <is>
+          <t>Hold wrapped 20 minutes. Refresh on the tawa.</t>
+        </is>
+      </c>
+      <c r="C24" s="31" t="n"/>
+      <c r="D24" s="31" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="21" t="inlineStr">
+        <is>
+          <t>Nutrition per portion</t>
+        </is>
+      </c>
+      <c r="B26" s="22" t="n"/>
+      <c r="C26" s="22" t="n"/>
+      <c r="D26" s="22" t="n"/>
+    </row>
+    <row r="27" ht="36" customHeight="1">
+      <c r="A27" s="12" t="inlineStr">
+        <is>
+          <t>kcal 318  ·  Protein 9 g  ·  Carbs 54 g  ·  Fat 8 g  ·  Fibre 8 g. Nutrition is a kitchen estimate from typical produce values, not a laboratory analysis.</t>
+        </is>
+      </c>
+      <c r="B27" s="49" t="n"/>
+      <c r="C27" s="49" t="n"/>
+      <c r="D27" s="49" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="24" t="inlineStr">
+        <is>
+          <t>Allergens</t>
+        </is>
+      </c>
+      <c r="B28" s="6" t="n"/>
+      <c r="C28" s="6" t="n"/>
+      <c r="D28" s="6" t="n"/>
+    </row>
+    <row r="29" ht="48" customHeight="1">
+      <c r="A29" s="25" t="inlineStr">
+        <is>
+          <t>Gluten (wheat) · Milk · Always verify labels; this card is a kitchen estimate, not a lab certificate.</t>
+        </is>
+      </c>
+      <c r="B29" s="26" t="n"/>
+      <c r="C29" s="26" t="n"/>
+      <c r="D29" s="26" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="24" t="inlineStr">
+        <is>
+          <t>Chef notes</t>
+        </is>
+      </c>
+      <c r="B30" s="6" t="n"/>
+      <c r="C30" s="6" t="n"/>
+      <c r="D30" s="6" t="n"/>
+    </row>
+    <row r="31" ht="72" customHeight="1">
+      <c r="A31" s="25" t="inlineStr">
+        <is>
+          <t>For Phulka / roti (national): keep the mix slightly drier than you think; wet mixes split or go greasy. Bloom hing in hot fat 20–30 seconds; raw hing tastes medicinal. Commercial hing is often cut with wheat flour — use a gluten-free hing if you must mark Gluten Free. Never cook tomato, tamarind, lemon, yogurt or milk in aluminium; use stainless steel, iron, clay or glass. Spice blends: read the packet. Many garam masalas hide onion or garlic powder.</t>
+        </is>
+      </c>
+      <c r="B31" s="26" t="n"/>
+      <c r="C31" s="26" t="n"/>
+      <c r="D31" s="26" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="50" t="inlineStr">
+        <is>
+          <t>Service notes</t>
+        </is>
+      </c>
+      <c r="B32" s="51" t="n"/>
+      <c r="C32" s="51" t="n"/>
+      <c r="D32" s="51" t="n"/>
+    </row>
+    <row r="33" ht="64" customHeight="1">
+      <c r="A33" s="12" t="inlineStr">
+        <is>
+          <t>Send to table wrapped. Do not stack in plastic or they sweat. Service temperature: Hot. Allergen label for this dish: Gluten (wheat); Milk; Always verify labels; this card is a kitchen estimate, not a lab certificate. State clearly: vegetarian, no onion, no garlic, no eggs, no meat, no fish. Nutrition on this card is an estimate for 1 portion of 4.</t>
+        </is>
+      </c>
+      <c r="B33" s="49" t="n"/>
+      <c r="C33" s="49" t="n"/>
+      <c r="D33" s="49" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="13">
+  <mergeCells count="26">
+    <mergeCell ref="A17:D17"/>
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="A29:D29"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="A28:D28"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="B19:D19"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="A30:D30"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="B20:D20"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="C12:D12"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="A17:D17"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="B19:D19"/>
-    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="A27:D27"/>
+    <mergeCell ref="B22:D22"/>
     <mergeCell ref="A3:D3"/>
+    <mergeCell ref="A26:D26"/>
     <mergeCell ref="B18:D18"/>
-    <mergeCell ref="C14:D14"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B21:D21"/>
+    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="A32:D32"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -2289,7 +2865,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D17"/>
+  <dimension ref="A1:D30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2301,7 +2877,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RECIPE CARD  ·  Naan (tandoor, no garlic)</t>
+          <t>Parslia Kitchen OS · RECIPE CARD · Naan (tandoor, no garlic)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2311,7 +2887,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Pan-India kitchen  ·  Bread  ·  Dishes cooked in homes all over India</t>
+          <t>Pure Prasad · No onion · No garlic · No eggs · No meat · No fish  ·  Pan-India  ·  Bread</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -2331,44 +2907,44 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="38" t="inlineStr">
         <is>
-          <t>Serves</t>
+          <t>YIELD</t>
         </is>
       </c>
       <c r="B5" s="38" t="inlineStr">
         <is>
-          <t>Prep</t>
+          <t>PORTION</t>
         </is>
       </c>
       <c r="C5" s="38" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>SERVICE</t>
         </is>
       </c>
       <c r="D5" s="38" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>TIME</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="39" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 portions</t>
         </is>
       </c>
       <c r="B6" s="39" t="inlineStr">
         <is>
-          <t>30 min</t>
+          <t>1 portion</t>
         </is>
       </c>
       <c r="C6" s="39" t="inlineStr">
         <is>
-          <t>15 min</t>
+          <t>Hot</t>
         </is>
       </c>
       <c r="D6" s="39" t="inlineStr">
         <is>
-          <t>45 min</t>
+          <t>Prep 30 min · Cook 15 min</t>
         </is>
       </c>
     </row>
@@ -2462,31 +3038,171 @@
       <c r="C16" s="45" t="n"/>
       <c r="D16" s="45" t="n"/>
     </row>
-    <row r="17" ht="36" customHeight="1">
+    <row r="17" ht="54" customHeight="1">
       <c r="A17" s="46" t="n">
         <v>1</v>
       </c>
       <c r="B17" s="47" t="inlineStr">
         <is>
-          <t>Rest dough. Stick in tandoor. Plain or butter naan without garlic.</t>
+          <t>Mise en place. Mix maida, yogurt, baking powder, salt and a little ghee. No garlic, no garlic butter. Rest 30 minutes. Clay tandoor or very hot steel tray.</t>
         </is>
       </c>
       <c r="C17" s="48" t="n"/>
       <c r="D17" s="48" t="n"/>
     </row>
+    <row r="18" ht="42" customHeight="1">
+      <c r="A18" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="B18" s="30" t="inlineStr">
+        <is>
+          <t>Divide. Roll teardrops 4 mm thick. Wet the back face if sticking to a tandoor wall.</t>
+        </is>
+      </c>
+      <c r="C18" s="31" t="n"/>
+      <c r="D18" s="31" t="n"/>
+    </row>
+    <row r="19" ht="42" customHeight="1">
+      <c r="A19" s="46" t="n">
+        <v>3</v>
+      </c>
+      <c r="B19" s="47" t="inlineStr">
+        <is>
+          <t>Bake until puffed with charred blisters, 60–90 seconds. Brush with plain ghee only.</t>
+        </is>
+      </c>
+      <c r="C19" s="48" t="n"/>
+      <c r="D19" s="48" t="n"/>
+    </row>
+    <row r="20" ht="36" customHeight="1">
+      <c r="A20" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="B20" s="30" t="inlineStr">
+        <is>
+          <t>Doneness: cooked through, blistered, soft. Serve at once.</t>
+        </is>
+      </c>
+      <c r="C20" s="31" t="n"/>
+      <c r="D20" s="31" t="n"/>
+    </row>
+    <row r="21" ht="36" customHeight="1">
+      <c r="A21" s="46" t="n">
+        <v>5</v>
+      </c>
+      <c r="B21" s="47" t="inlineStr">
+        <is>
+          <t>Hold 10 minutes in a cloth. Label gluten and milk.</t>
+        </is>
+      </c>
+      <c r="C21" s="48" t="n"/>
+      <c r="D21" s="48" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="21" t="inlineStr">
+        <is>
+          <t>Nutrition per portion</t>
+        </is>
+      </c>
+      <c r="B23" s="22" t="n"/>
+      <c r="C23" s="22" t="n"/>
+      <c r="D23" s="22" t="n"/>
+    </row>
+    <row r="24" ht="36" customHeight="1">
+      <c r="A24" s="12" t="inlineStr">
+        <is>
+          <t>kcal 228  ·  Protein 6 g  ·  Carbs 48 g  ·  Fat 1 g  ·  Fibre 2 g. Nutrition is a kitchen estimate from typical produce values, not a laboratory analysis.</t>
+        </is>
+      </c>
+      <c r="B24" s="49" t="n"/>
+      <c r="C24" s="49" t="n"/>
+      <c r="D24" s="49" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="24" t="inlineStr">
+        <is>
+          <t>Allergens</t>
+        </is>
+      </c>
+      <c r="B25" s="6" t="n"/>
+      <c r="C25" s="6" t="n"/>
+      <c r="D25" s="6" t="n"/>
+    </row>
+    <row r="26" ht="48" customHeight="1">
+      <c r="A26" s="25" t="inlineStr">
+        <is>
+          <t>Gluten (wheat) · Milk · Always verify labels; this card is a kitchen estimate, not a lab certificate.</t>
+        </is>
+      </c>
+      <c r="B26" s="26" t="n"/>
+      <c r="C26" s="26" t="n"/>
+      <c r="D26" s="26" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="24" t="inlineStr">
+        <is>
+          <t>Chef notes</t>
+        </is>
+      </c>
+      <c r="B27" s="6" t="n"/>
+      <c r="C27" s="6" t="n"/>
+      <c r="D27" s="6" t="n"/>
+    </row>
+    <row r="28" ht="72" customHeight="1">
+      <c r="A28" s="25" t="inlineStr">
+        <is>
+          <t>For Naan (tandoor, no garlic): keep the mix slightly drier than you think; wet mixes split or go greasy. Bloom hing in hot fat 20–30 seconds; raw hing tastes medicinal. Commercial hing is often cut with wheat flour — use a gluten-free hing if you must mark Gluten Free. Never cook tomato, tamarind, lemon, yogurt or milk in aluminium; use stainless steel, iron, clay or glass. Spice blends: read the packet. Many garam masalas hide onion or garlic powder.</t>
+        </is>
+      </c>
+      <c r="B28" s="26" t="n"/>
+      <c r="C28" s="26" t="n"/>
+      <c r="D28" s="26" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="50" t="inlineStr">
+        <is>
+          <t>Service notes</t>
+        </is>
+      </c>
+      <c r="B29" s="51" t="n"/>
+      <c r="C29" s="51" t="n"/>
+      <c r="D29" s="51" t="n"/>
+    </row>
+    <row r="30" ht="64" customHeight="1">
+      <c r="A30" s="12" t="inlineStr">
+        <is>
+          <t>Send to table wrapped. Do not stack in plastic or they sweat. Service temperature: Hot. Allergen label for this dish: Gluten (wheat); Milk; Always verify labels; this card is a kitchen estimate, not a lab certificate. State clearly: vegetarian, no onion, no garlic, no eggs, no meat, no fish. Nutrition on this card is an estimate for 1 portion of 4.</t>
+        </is>
+      </c>
+      <c r="B30" s="49" t="n"/>
+      <c r="C30" s="49" t="n"/>
+      <c r="D30" s="49" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="11">
+  <mergeCells count="23">
+    <mergeCell ref="A23:D23"/>
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="B17:D17"/>
+    <mergeCell ref="A29:D29"/>
+    <mergeCell ref="A28:D28"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="B19:D19"/>
+    <mergeCell ref="A30:D30"/>
+    <mergeCell ref="A15:D15"/>
+    <mergeCell ref="A24:D24"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B20:D20"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="C12:D12"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="A25:D25"/>
+    <mergeCell ref="B16:D16"/>
+    <mergeCell ref="A27:D27"/>
     <mergeCell ref="A3:D3"/>
-    <mergeCell ref="B17:D17"/>
-    <mergeCell ref="A15:D15"/>
+    <mergeCell ref="A26:D26"/>
+    <mergeCell ref="B18:D18"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="B16:D16"/>
+    <mergeCell ref="B21:D21"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -2500,7 +3216,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D18"/>
+  <dimension ref="A1:D31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2512,7 +3228,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RECIPE CARD  ·  Jeera rice (national, no onion)</t>
+          <t>Parslia Kitchen OS · RECIPE CARD · Jeera rice (national, no onion)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2522,7 +3238,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Pan-India kitchen  ·  Bread  ·  Dishes cooked in homes all over India</t>
+          <t>Pure Prasad · No onion · No garlic · No eggs · No meat · No fish  ·  Pan-India  ·  Bread</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -2542,44 +3258,44 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="38" t="inlineStr">
         <is>
-          <t>Serves</t>
+          <t>YIELD</t>
         </is>
       </c>
       <c r="B5" s="38" t="inlineStr">
         <is>
-          <t>Prep</t>
+          <t>PORTION</t>
         </is>
       </c>
       <c r="C5" s="38" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>SERVICE</t>
         </is>
       </c>
       <c r="D5" s="38" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>TIME</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="39" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 portions</t>
         </is>
       </c>
       <c r="B6" s="39" t="inlineStr">
         <is>
-          <t>10 min</t>
+          <t>1 portion</t>
         </is>
       </c>
       <c r="C6" s="39" t="inlineStr">
         <is>
-          <t>20 min</t>
+          <t>Hot</t>
         </is>
       </c>
       <c r="D6" s="39" t="inlineStr">
         <is>
-          <t>30 min</t>
+          <t>Prep 10 min · Cook 20 min</t>
         </is>
       </c>
     </row>
@@ -2691,32 +3407,172 @@
       <c r="C17" s="45" t="n"/>
       <c r="D17" s="45" t="n"/>
     </row>
-    <row r="18" ht="36" customHeight="1">
+    <row r="18" ht="42" customHeight="1">
       <c r="A18" s="46" t="n">
         <v>1</v>
       </c>
       <c r="B18" s="47" t="inlineStr">
         <is>
-          <t>Temper whole spices. Rice. Water. Simmer.</t>
+          <t>Mise en place. Rinse 2 cups basmati until the water runs clearer. Soak 15 minutes. Drain. Steel pot — never aluminium. No fried onion.</t>
         </is>
       </c>
       <c r="C18" s="48" t="n"/>
       <c r="D18" s="48" t="n"/>
     </row>
+    <row r="19" ht="42" customHeight="1">
+      <c r="A19" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="B19" s="30" t="inlineStr">
+        <is>
+          <t>Heat ghee. Bloom 1 tsp cumin, 2 bay leaves and 4 cloves 20–30 seconds.</t>
+        </is>
+      </c>
+      <c r="C19" s="31" t="n"/>
+      <c r="D19" s="31" t="n"/>
+    </row>
+    <row r="20" ht="54" customHeight="1">
+      <c r="A20" s="46" t="n">
+        <v>3</v>
+      </c>
+      <c r="B20" s="47" t="inlineStr">
+        <is>
+          <t>Add rice. Toss 1 minute. Add measured water and salt (about 1.75 cups water per cup rice for this soak). Bring to a boil. Cover. Low heat 12 minutes. Rest 5 minutes. Fluff.</t>
+        </is>
+      </c>
+      <c r="C20" s="48" t="n"/>
+      <c r="D20" s="48" t="n"/>
+    </row>
+    <row r="21" ht="36" customHeight="1">
+      <c r="A21" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="B21" s="30" t="inlineStr">
+        <is>
+          <t>Doneness: grains separate, cumin visible, no wet clump. Serve hot.</t>
+        </is>
+      </c>
+      <c r="C21" s="31" t="n"/>
+      <c r="D21" s="31" t="n"/>
+    </row>
+    <row r="22" ht="36" customHeight="1">
+      <c r="A22" s="46" t="n">
+        <v>5</v>
+      </c>
+      <c r="B22" s="47" t="inlineStr">
+        <is>
+          <t>Hold covered 20 minutes. Steam only — do not stir hard.</t>
+        </is>
+      </c>
+      <c r="C22" s="48" t="n"/>
+      <c r="D22" s="48" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="21" t="inlineStr">
+        <is>
+          <t>Nutrition per portion</t>
+        </is>
+      </c>
+      <c r="B24" s="22" t="n"/>
+      <c r="C24" s="22" t="n"/>
+      <c r="D24" s="22" t="n"/>
+    </row>
+    <row r="25" ht="36" customHeight="1">
+      <c r="A25" s="12" t="inlineStr">
+        <is>
+          <t>kcal 104  ·  Protein 3 g  ·  Carbs 14 g  ·  Fat 4 g  ·  Fibre 2 g. Nutrition is a kitchen estimate from typical produce values, not a laboratory analysis.</t>
+        </is>
+      </c>
+      <c r="B25" s="49" t="n"/>
+      <c r="C25" s="49" t="n"/>
+      <c r="D25" s="49" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="24" t="inlineStr">
+        <is>
+          <t>Allergens</t>
+        </is>
+      </c>
+      <c r="B26" s="6" t="n"/>
+      <c r="C26" s="6" t="n"/>
+      <c r="D26" s="6" t="n"/>
+    </row>
+    <row r="27" ht="48" customHeight="1">
+      <c r="A27" s="25" t="inlineStr">
+        <is>
+          <t>Milk · Always verify labels; this card is a kitchen estimate, not a lab certificate.</t>
+        </is>
+      </c>
+      <c r="B27" s="26" t="n"/>
+      <c r="C27" s="26" t="n"/>
+      <c r="D27" s="26" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="24" t="inlineStr">
+        <is>
+          <t>Chef notes</t>
+        </is>
+      </c>
+      <c r="B28" s="6" t="n"/>
+      <c r="C28" s="6" t="n"/>
+      <c r="D28" s="6" t="n"/>
+    </row>
+    <row r="29" ht="72" customHeight="1">
+      <c r="A29" s="25" t="inlineStr">
+        <is>
+          <t>For Jeera rice (national, no onion): keep the mix slightly drier than you think; wet mixes split or go greasy. Bloom hing in hot fat 20–30 seconds; raw hing tastes medicinal. Commercial hing is often cut with wheat flour — use a gluten-free hing if you must mark Gluten Free. Never cook tomato, tamarind, lemon, yogurt or milk in aluminium; use stainless steel, iron, clay or glass. Spice blends: read the packet. Many garam masalas hide onion or garlic powder.</t>
+        </is>
+      </c>
+      <c r="B29" s="26" t="n"/>
+      <c r="C29" s="26" t="n"/>
+      <c r="D29" s="26" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="50" t="inlineStr">
+        <is>
+          <t>Service notes</t>
+        </is>
+      </c>
+      <c r="B30" s="51" t="n"/>
+      <c r="C30" s="51" t="n"/>
+      <c r="D30" s="51" t="n"/>
+    </row>
+    <row r="31" ht="64" customHeight="1">
+      <c r="A31" s="12" t="inlineStr">
+        <is>
+          <t>Send to table wrapped. Do not stack in plastic or they sweat. Service temperature: Hot. Allergen label for this dish: Milk; Always verify labels; this card is a kitchen estimate, not a lab certificate. State clearly: vegetarian, no onion, no garlic, no eggs, no meat, no fish. Nutrition on this card is an estimate for 1 portion of 4.</t>
+        </is>
+      </c>
+      <c r="B31" s="49" t="n"/>
+      <c r="C31" s="49" t="n"/>
+      <c r="D31" s="49" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="12">
+  <mergeCells count="24">
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="B17:D17"/>
+    <mergeCell ref="A29:D29"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="A28:D28"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="B19:D19"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="A30:D30"/>
+    <mergeCell ref="A24:D24"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B20:D20"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="C12:D12"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="A25:D25"/>
+    <mergeCell ref="A16:D16"/>
+    <mergeCell ref="A27:D27"/>
+    <mergeCell ref="B22:D22"/>
     <mergeCell ref="A3:D3"/>
-    <mergeCell ref="B17:D17"/>
+    <mergeCell ref="A26:D26"/>
     <mergeCell ref="B18:D18"/>
-    <mergeCell ref="C14:D14"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="A16:D16"/>
+    <mergeCell ref="B21:D21"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -2730,7 +3586,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D16"/>
+  <dimension ref="A1:D30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2742,7 +3598,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RECIPE CARD  ·  Gulab jamun (khoya, no onion)</t>
+          <t>Parslia Kitchen OS · RECIPE CARD · Gulab jamun (khoya, no onion)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2752,7 +3608,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Pan-India kitchen  ·  Sweet  ·  Dishes cooked in homes all over India</t>
+          <t>Pure Prasad · No onion · No garlic · No eggs · No meat · No fish  ·  Pan-India  ·  Sweet</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -2772,44 +3628,44 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="38" t="inlineStr">
         <is>
-          <t>Serves</t>
+          <t>YIELD</t>
         </is>
       </c>
       <c r="B5" s="38" t="inlineStr">
         <is>
-          <t>Prep</t>
+          <t>PORTION</t>
         </is>
       </c>
       <c r="C5" s="38" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>SERVICE</t>
         </is>
       </c>
       <c r="D5" s="38" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>TIME</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="39" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 portions</t>
         </is>
       </c>
       <c r="B6" s="39" t="inlineStr">
         <is>
-          <t>30 min</t>
+          <t>1 portion</t>
         </is>
       </c>
       <c r="C6" s="39" t="inlineStr">
         <is>
-          <t>25 min</t>
+          <t>Hot</t>
         </is>
       </c>
       <c r="D6" s="39" t="inlineStr">
         <is>
-          <t>55 min</t>
+          <t>Prep 30 min · Cook 25 min</t>
         </is>
       </c>
     </row>
@@ -2885,29 +3741,182 @@
       <c r="C15" s="45" t="n"/>
       <c r="D15" s="45" t="n"/>
     </row>
-    <row r="16" ht="36" customHeight="1">
+    <row r="16" ht="54" customHeight="1">
       <c r="A16" s="46" t="n">
         <v>1</v>
       </c>
       <c r="B16" s="47" t="inlineStr">
         <is>
-          <t>Fry on low. Soak.</t>
+          <t>Mise en place. Mix khoya and a little maida to a smooth dough — no cracks, no extra flour. Sugar syrup with rose and cardamom, one-string, warm. Steel kadhai of ghee — never aluminium.</t>
         </is>
       </c>
       <c r="C16" s="48" t="n"/>
       <c r="D16" s="48" t="n"/>
     </row>
+    <row r="17" ht="36" customHeight="1">
+      <c r="A17" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="B17" s="30" t="inlineStr">
+        <is>
+          <t>Shape 16 smooth balls. If they crack, knead with a drop of milk.</t>
+        </is>
+      </c>
+      <c r="C17" s="31" t="n"/>
+      <c r="D17" s="31" t="n"/>
+    </row>
+    <row r="18" ht="42" customHeight="1">
+      <c r="A18" s="46" t="n">
+        <v>3</v>
+      </c>
+      <c r="B18" s="47" t="inlineStr">
+        <is>
+          <t>Fry on low-medium, 6–8 minutes, turning, until deep brown. High heat colours the outside and leaves a raw centre.</t>
+        </is>
+      </c>
+      <c r="C18" s="48" t="n"/>
+      <c r="D18" s="48" t="n"/>
+    </row>
+    <row r="19" ht="36" customHeight="1">
+      <c r="A19" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="B19" s="30" t="inlineStr">
+        <is>
+          <t>Drain 30 seconds. Soak in warm syrup 30 minutes, turning once.</t>
+        </is>
+      </c>
+      <c r="C19" s="31" t="n"/>
+      <c r="D19" s="31" t="n"/>
+    </row>
+    <row r="20" ht="42" customHeight="1">
+      <c r="A20" s="46" t="n">
+        <v>5</v>
+      </c>
+      <c r="B20" s="47" t="inlineStr">
+        <is>
+          <t>Doneness: balls swollen, syrup in the centre, no doughy core. Serve warm, 2 per portion.</t>
+        </is>
+      </c>
+      <c r="C20" s="48" t="n"/>
+      <c r="D20" s="48" t="n"/>
+    </row>
+    <row r="21" ht="36" customHeight="1">
+      <c r="A21" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="B21" s="30" t="inlineStr">
+        <is>
+          <t>Hold in syrup. Label milk and gluten.</t>
+        </is>
+      </c>
+      <c r="C21" s="31" t="n"/>
+      <c r="D21" s="31" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="21" t="inlineStr">
+        <is>
+          <t>Nutrition per portion</t>
+        </is>
+      </c>
+      <c r="B23" s="22" t="n"/>
+      <c r="C23" s="22" t="n"/>
+      <c r="D23" s="22" t="n"/>
+    </row>
+    <row r="24" ht="36" customHeight="1">
+      <c r="A24" s="12" t="inlineStr">
+        <is>
+          <t>kcal 0  ·  Protein 0 g  ·  Carbs 0 g  ·  Fat 0 g  ·  Fibre 0 g. Nutrition is a kitchen estimate from typical produce values, not a laboratory analysis.</t>
+        </is>
+      </c>
+      <c r="B24" s="49" t="n"/>
+      <c r="C24" s="49" t="n"/>
+      <c r="D24" s="49" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="24" t="inlineStr">
+        <is>
+          <t>Allergens</t>
+        </is>
+      </c>
+      <c r="B25" s="6" t="n"/>
+      <c r="C25" s="6" t="n"/>
+      <c r="D25" s="6" t="n"/>
+    </row>
+    <row r="26" ht="48" customHeight="1">
+      <c r="A26" s="25" t="inlineStr">
+        <is>
+          <t>Gluten (wheat) · Milk · Always verify labels; this card is a kitchen estimate, not a lab certificate.</t>
+        </is>
+      </c>
+      <c r="B26" s="26" t="n"/>
+      <c r="C26" s="26" t="n"/>
+      <c r="D26" s="26" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="24" t="inlineStr">
+        <is>
+          <t>Chef notes</t>
+        </is>
+      </c>
+      <c r="B27" s="6" t="n"/>
+      <c r="C27" s="6" t="n"/>
+      <c r="D27" s="6" t="n"/>
+    </row>
+    <row r="28" ht="72" customHeight="1">
+      <c r="A28" s="25" t="inlineStr">
+        <is>
+          <t>For Gulab jamun (khoya, no onion): keep the mix slightly drier than you think; wet mixes split or go greasy. Bloom hing in hot fat 20–30 seconds; raw hing tastes medicinal. Commercial hing is often cut with wheat flour — use a gluten-free hing if you must mark Gluten Free. Never cook tomato, tamarind, lemon, yogurt or milk in aluminium; use stainless steel, iron, clay or glass. Spice blends: read the packet. Many garam masalas hide onion or garlic powder.</t>
+        </is>
+      </c>
+      <c r="B28" s="26" t="n"/>
+      <c r="C28" s="26" t="n"/>
+      <c r="D28" s="26" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="50" t="inlineStr">
+        <is>
+          <t>Service notes</t>
+        </is>
+      </c>
+      <c r="B29" s="51" t="n"/>
+      <c r="C29" s="51" t="n"/>
+      <c r="D29" s="51" t="n"/>
+    </row>
+    <row r="30" ht="64" customHeight="1">
+      <c r="A30" s="12" t="inlineStr">
+        <is>
+          <t>Cut even portions. Garnish with nuts only if the allergen card allows. Service temperature: Hot. Allergen label for this dish: Gluten (wheat); Milk; Always verify labels; this card is a kitchen estimate, not a lab certificate. State clearly: vegetarian, no onion, no garlic, no eggs, no meat, no fish. Nutrition on this card is an estimate for 1 portion of 4.</t>
+        </is>
+      </c>
+      <c r="B30" s="49" t="n"/>
+      <c r="C30" s="49" t="n"/>
+      <c r="D30" s="49" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="23">
+    <mergeCell ref="A23:D23"/>
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="B17:D17"/>
+    <mergeCell ref="A29:D29"/>
+    <mergeCell ref="A28:D28"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="B19:D19"/>
+    <mergeCell ref="A30:D30"/>
+    <mergeCell ref="A24:D24"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B15:D15"/>
+    <mergeCell ref="B20:D20"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="C12:D12"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="A25:D25"/>
+    <mergeCell ref="B16:D16"/>
+    <mergeCell ref="A27:D27"/>
     <mergeCell ref="A3:D3"/>
+    <mergeCell ref="A26:D26"/>
+    <mergeCell ref="B18:D18"/>
+    <mergeCell ref="B21:D21"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="B15:D15"/>
-    <mergeCell ref="B16:D16"/>
     <mergeCell ref="A14:D14"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2922,7 +3931,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D16"/>
+  <dimension ref="A1:D29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2934,7 +3943,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RECIPE CARD  ·  Jalebi (fermented batter)</t>
+          <t>Parslia Kitchen OS · RECIPE CARD · Jalebi (fermented batter)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2944,7 +3953,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Pan-India kitchen  ·  Sweet  ·  Dishes cooked in homes all over India</t>
+          <t>Pure Prasad · No onion · No garlic · No eggs · No meat · No fish  ·  Pan-India  ·  Sweet</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -2964,44 +3973,44 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="38" t="inlineStr">
         <is>
-          <t>Serves</t>
+          <t>YIELD</t>
         </is>
       </c>
       <c r="B5" s="38" t="inlineStr">
         <is>
-          <t>Prep</t>
+          <t>PORTION</t>
         </is>
       </c>
       <c r="C5" s="38" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>SERVICE</t>
         </is>
       </c>
       <c r="D5" s="38" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>TIME</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="39" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 portions</t>
         </is>
       </c>
       <c r="B6" s="39" t="inlineStr">
         <is>
-          <t>20 min</t>
+          <t>1 portion</t>
         </is>
       </c>
       <c r="C6" s="39" t="inlineStr">
         <is>
-          <t>25 min</t>
+          <t>Hot</t>
         </is>
       </c>
       <c r="D6" s="39" t="inlineStr">
         <is>
-          <t>45 min</t>
+          <t>Prep 20 min · Cook 25 min</t>
         </is>
       </c>
     </row>
@@ -3077,29 +4086,169 @@
       <c r="C15" s="45" t="n"/>
       <c r="D15" s="45" t="n"/>
     </row>
-    <row r="16" ht="36" customHeight="1">
+    <row r="16" ht="42" customHeight="1">
       <c r="A16" s="46" t="n">
         <v>1</v>
       </c>
       <c r="B16" s="47" t="inlineStr">
         <is>
-          <t>Pipe coils. Fry. Dip.</t>
+          <t>Mise en place. Fermented maida batter in a piping cloth. One-string saffron sugar syrup, warm. Steel kadhai of ghee — never aluminium.</t>
         </is>
       </c>
       <c r="C16" s="48" t="n"/>
       <c r="D16" s="48" t="n"/>
     </row>
+    <row r="17" ht="42" customHeight="1">
+      <c r="A17" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="B17" s="30" t="inlineStr">
+        <is>
+          <t>Pipe tight coils into 170 C fat. Fry until crisp and orange-gold, 1–2 minutes a side.</t>
+        </is>
+      </c>
+      <c r="C17" s="31" t="n"/>
+      <c r="D17" s="31" t="n"/>
+    </row>
+    <row r="18" ht="36" customHeight="1">
+      <c r="A18" s="46" t="n">
+        <v>3</v>
+      </c>
+      <c r="B18" s="47" t="inlineStr">
+        <is>
+          <t>Dip in syrup 20–30 seconds. Lift. Drain on a steel rack.</t>
+        </is>
+      </c>
+      <c r="C18" s="48" t="n"/>
+      <c r="D18" s="48" t="n"/>
+    </row>
+    <row r="19" ht="42" customHeight="1">
+      <c r="A19" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="B19" s="30" t="inlineStr">
+        <is>
+          <t>Doneness: crisp, syrup in the tunnels, not soggy. Serve hot or at room temperature within 2 hours.</t>
+        </is>
+      </c>
+      <c r="C19" s="31" t="n"/>
+      <c r="D19" s="31" t="n"/>
+    </row>
+    <row r="20" ht="36" customHeight="1">
+      <c r="A20" s="46" t="n">
+        <v>5</v>
+      </c>
+      <c r="B20" s="47" t="inlineStr">
+        <is>
+          <t>Label gluten. Do not hold in a closed box or they sweat.</t>
+        </is>
+      </c>
+      <c r="C20" s="48" t="n"/>
+      <c r="D20" s="48" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="21" t="inlineStr">
+        <is>
+          <t>Nutrition per portion</t>
+        </is>
+      </c>
+      <c r="B22" s="22" t="n"/>
+      <c r="C22" s="22" t="n"/>
+      <c r="D22" s="22" t="n"/>
+    </row>
+    <row r="23" ht="36" customHeight="1">
+      <c r="A23" s="12" t="inlineStr">
+        <is>
+          <t>kcal 0  ·  Protein 0 g  ·  Carbs 0 g  ·  Fat 0 g  ·  Fibre 0 g. Nutrition is a kitchen estimate from typical produce values, not a laboratory analysis.</t>
+        </is>
+      </c>
+      <c r="B23" s="49" t="n"/>
+      <c r="C23" s="49" t="n"/>
+      <c r="D23" s="49" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="24" t="inlineStr">
+        <is>
+          <t>Allergens</t>
+        </is>
+      </c>
+      <c r="B24" s="6" t="n"/>
+      <c r="C24" s="6" t="n"/>
+      <c r="D24" s="6" t="n"/>
+    </row>
+    <row r="25" ht="48" customHeight="1">
+      <c r="A25" s="25" t="inlineStr">
+        <is>
+          <t>Gluten (wheat) · Milk · Always verify labels; this card is a kitchen estimate, not a lab certificate.</t>
+        </is>
+      </c>
+      <c r="B25" s="26" t="n"/>
+      <c r="C25" s="26" t="n"/>
+      <c r="D25" s="26" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="24" t="inlineStr">
+        <is>
+          <t>Chef notes</t>
+        </is>
+      </c>
+      <c r="B26" s="6" t="n"/>
+      <c r="C26" s="6" t="n"/>
+      <c r="D26" s="6" t="n"/>
+    </row>
+    <row r="27" ht="72" customHeight="1">
+      <c r="A27" s="25" t="inlineStr">
+        <is>
+          <t>For Jalebi (fermented batter): keep the mix slightly drier than you think; wet mixes split or go greasy. Bloom hing in hot fat 20–30 seconds; raw hing tastes medicinal. Commercial hing is often cut with wheat flour — use a gluten-free hing if you must mark Gluten Free. Never cook tomato, tamarind, lemon, yogurt or milk in aluminium; use stainless steel, iron, clay or glass. Spice blends: read the packet. Many garam masalas hide onion or garlic powder.</t>
+        </is>
+      </c>
+      <c r="B27" s="26" t="n"/>
+      <c r="C27" s="26" t="n"/>
+      <c r="D27" s="26" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="50" t="inlineStr">
+        <is>
+          <t>Service notes</t>
+        </is>
+      </c>
+      <c r="B28" s="51" t="n"/>
+      <c r="C28" s="51" t="n"/>
+      <c r="D28" s="51" t="n"/>
+    </row>
+    <row r="29" ht="64" customHeight="1">
+      <c r="A29" s="12" t="inlineStr">
+        <is>
+          <t>Cut even portions. Garnish with nuts only if the allergen card allows. Service temperature: Hot. Allergen label for this dish: Gluten (wheat); Milk; Always verify labels; this card is a kitchen estimate, not a lab certificate. State clearly: vegetarian, no onion, no garlic, no eggs, no meat, no fish. Nutrition on this card is an estimate for 1 portion of 4.</t>
+        </is>
+      </c>
+      <c r="B29" s="49" t="n"/>
+      <c r="C29" s="49" t="n"/>
+      <c r="D29" s="49" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="22">
+    <mergeCell ref="A23:D23"/>
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="A22:D22"/>
+    <mergeCell ref="B17:D17"/>
+    <mergeCell ref="A29:D29"/>
+    <mergeCell ref="A28:D28"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="B19:D19"/>
+    <mergeCell ref="A24:D24"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B15:D15"/>
+    <mergeCell ref="B20:D20"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="C12:D12"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="A25:D25"/>
+    <mergeCell ref="B16:D16"/>
+    <mergeCell ref="A27:D27"/>
     <mergeCell ref="A3:D3"/>
+    <mergeCell ref="A26:D26"/>
+    <mergeCell ref="B18:D18"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="B15:D15"/>
-    <mergeCell ref="B16:D16"/>
     <mergeCell ref="A14:D14"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3114,7 +4263,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D19"/>
+  <dimension ref="A1:D32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3126,7 +4275,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RECIPE CARD  ·  Besan ladoo (national)</t>
+          <t>Parslia Kitchen OS · RECIPE CARD · Besan ladoo (national)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3136,7 +4285,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Pan-India kitchen  ·  Sweet  ·  Dishes cooked in homes all over India</t>
+          <t>Pure Prasad · No onion · No garlic · No eggs · No meat · No fish  ·  Pan-India  ·  Sweet</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -3156,44 +4305,44 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="38" t="inlineStr">
         <is>
-          <t>Serves</t>
+          <t>YIELD</t>
         </is>
       </c>
       <c r="B5" s="38" t="inlineStr">
         <is>
-          <t>Prep</t>
+          <t>PORTION</t>
         </is>
       </c>
       <c r="C5" s="38" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>SERVICE</t>
         </is>
       </c>
       <c r="D5" s="38" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>TIME</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="39" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 portions</t>
         </is>
       </c>
       <c r="B6" s="39" t="inlineStr">
         <is>
-          <t>15 min</t>
+          <t>1 portion</t>
         </is>
       </c>
       <c r="C6" s="39" t="inlineStr">
         <is>
-          <t>30 min</t>
+          <t>Hot</t>
         </is>
       </c>
       <c r="D6" s="39" t="inlineStr">
         <is>
-          <t>45 min</t>
+          <t>Prep 15 min · Cook 30 min</t>
         </is>
       </c>
     </row>
@@ -3323,33 +4472,173 @@
       <c r="C18" s="45" t="n"/>
       <c r="D18" s="45" t="n"/>
     </row>
-    <row r="19" ht="36" customHeight="1">
+    <row r="19" ht="42" customHeight="1">
       <c r="A19" s="46" t="n">
         <v>1</v>
       </c>
       <c r="B19" s="47" t="inlineStr">
         <is>
-          <t>Roast. Mix. Shape.</t>
+          <t>Mise en place. Weigh 2 cups besan, 1 cup ghee, 1 cup powdered sugar, cardamom, nuts. Heavy steel kadhai — never aluminium.</t>
         </is>
       </c>
       <c r="C19" s="48" t="n"/>
       <c r="D19" s="48" t="n"/>
     </row>
+    <row r="20" ht="42" customHeight="1">
+      <c r="A20" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="B20" s="30" t="inlineStr">
+        <is>
+          <t>Roast besan in ghee on low 15–20 minutes until the colour is deep gold and the raw smell is gone. Stir without pause.</t>
+        </is>
+      </c>
+      <c r="C20" s="31" t="n"/>
+      <c r="D20" s="31" t="n"/>
+    </row>
+    <row r="21" ht="42" customHeight="1">
+      <c r="A21" s="46" t="n">
+        <v>3</v>
+      </c>
+      <c r="B21" s="47" t="inlineStr">
+        <is>
+          <t>Cool 10 minutes. Mix sugar, cardamom and nuts. Shape 30 g ladoos while warm.</t>
+        </is>
+      </c>
+      <c r="C21" s="48" t="n"/>
+      <c r="D21" s="48" t="n"/>
+    </row>
+    <row r="22" ht="36" customHeight="1">
+      <c r="A22" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="B22" s="30" t="inlineStr">
+        <is>
+          <t>Doneness: holds shape, no raw besan. Cool fully.</t>
+        </is>
+      </c>
+      <c r="C22" s="31" t="n"/>
+      <c r="D22" s="31" t="n"/>
+    </row>
+    <row r="23" ht="42" customHeight="1">
+      <c r="A23" s="46" t="n">
+        <v>5</v>
+      </c>
+      <c r="B23" s="47" t="inlineStr">
+        <is>
+          <t>Store in a tin. Label milk and tree nuts. Besan is chickpea — still verify hing is not in this mix.</t>
+        </is>
+      </c>
+      <c r="C23" s="48" t="n"/>
+      <c r="D23" s="48" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="21" t="inlineStr">
+        <is>
+          <t>Nutrition per portion</t>
+        </is>
+      </c>
+      <c r="B25" s="22" t="n"/>
+      <c r="C25" s="22" t="n"/>
+      <c r="D25" s="22" t="n"/>
+    </row>
+    <row r="26" ht="36" customHeight="1">
+      <c r="A26" s="12" t="inlineStr">
+        <is>
+          <t>kcal 715  ·  Protein 13 g  ·  Carbs 72 g  ·  Fat 41 g  ·  Fibre 7 g. Nutrition is a kitchen estimate from typical produce values, not a laboratory analysis.</t>
+        </is>
+      </c>
+      <c r="B26" s="49" t="n"/>
+      <c r="C26" s="49" t="n"/>
+      <c r="D26" s="49" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="24" t="inlineStr">
+        <is>
+          <t>Allergens</t>
+        </is>
+      </c>
+      <c r="B27" s="6" t="n"/>
+      <c r="C27" s="6" t="n"/>
+      <c r="D27" s="6" t="n"/>
+    </row>
+    <row r="28" ht="48" customHeight="1">
+      <c r="A28" s="25" t="inlineStr">
+        <is>
+          <t>Gluten (wheat) · Milk · Always verify labels; this card is a kitchen estimate, not a lab certificate.</t>
+        </is>
+      </c>
+      <c r="B28" s="26" t="n"/>
+      <c r="C28" s="26" t="n"/>
+      <c r="D28" s="26" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="24" t="inlineStr">
+        <is>
+          <t>Chef notes</t>
+        </is>
+      </c>
+      <c r="B29" s="6" t="n"/>
+      <c r="C29" s="6" t="n"/>
+      <c r="D29" s="6" t="n"/>
+    </row>
+    <row r="30" ht="72" customHeight="1">
+      <c r="A30" s="25" t="inlineStr">
+        <is>
+          <t>For Besan ladoo (national): keep the mix slightly drier than you think; wet mixes split or go greasy. Bloom hing in hot fat 20–30 seconds; raw hing tastes medicinal. Commercial hing is often cut with wheat flour — use a gluten-free hing if you must mark Gluten Free. Never cook tomato, tamarind, lemon, yogurt or milk in aluminium; use stainless steel, iron, clay or glass. Spice blends: read the packet. Many garam masalas hide onion or garlic powder. Cook or roast besan until the raw smell is gone.</t>
+        </is>
+      </c>
+      <c r="B30" s="26" t="n"/>
+      <c r="C30" s="26" t="n"/>
+      <c r="D30" s="26" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="50" t="inlineStr">
+        <is>
+          <t>Service notes</t>
+        </is>
+      </c>
+      <c r="B31" s="51" t="n"/>
+      <c r="C31" s="51" t="n"/>
+      <c r="D31" s="51" t="n"/>
+    </row>
+    <row r="32" ht="64" customHeight="1">
+      <c r="A32" s="12" t="inlineStr">
+        <is>
+          <t>Cut even portions. Garnish with nuts only if the allergen card allows. Service temperature: Hot. Allergen label for this dish: Gluten (wheat); Milk; Always verify labels; this card is a kitchen estimate, not a lab certificate. State clearly: vegetarian, no onion, no garlic, no eggs, no meat, no fish. Nutrition on this card is an estimate for 1 portion of 4.</t>
+        </is>
+      </c>
+      <c r="B32" s="49" t="n"/>
+      <c r="C32" s="49" t="n"/>
+      <c r="D32" s="49" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="13">
+  <mergeCells count="25">
+    <mergeCell ref="A17:D17"/>
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="A29:D29"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="A28:D28"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="B19:D19"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="A30:D30"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B20:D20"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="C12:D12"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="A17:D17"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="B19:D19"/>
-    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="A25:D25"/>
+    <mergeCell ref="A27:D27"/>
+    <mergeCell ref="B22:D22"/>
     <mergeCell ref="A3:D3"/>
+    <mergeCell ref="A26:D26"/>
     <mergeCell ref="B18:D18"/>
-    <mergeCell ref="C14:D14"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B21:D21"/>
+    <mergeCell ref="A32:D32"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -3363,7 +4652,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D16"/>
+  <dimension ref="A1:D29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3375,7 +4664,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RECIPE CARD  ·  Kheer (rice milk, national)</t>
+          <t>Parslia Kitchen OS · RECIPE CARD · Kheer (rice milk, national)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3385,7 +4674,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Pan-India kitchen  ·  Dessert  ·  Dishes cooked in homes all over India</t>
+          <t>Pure Prasad · No onion · No garlic · No eggs · No meat · No fish  ·  Pan-India  ·  Dessert</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -3405,44 +4694,44 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="38" t="inlineStr">
         <is>
-          <t>Serves</t>
+          <t>YIELD</t>
         </is>
       </c>
       <c r="B5" s="38" t="inlineStr">
         <is>
-          <t>Prep</t>
+          <t>PORTION</t>
         </is>
       </c>
       <c r="C5" s="38" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>SERVICE</t>
         </is>
       </c>
       <c r="D5" s="38" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>TIME</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="39" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 portions</t>
         </is>
       </c>
       <c r="B6" s="39" t="inlineStr">
         <is>
-          <t>10 min</t>
+          <t>1 portion</t>
         </is>
       </c>
       <c r="C6" s="39" t="inlineStr">
         <is>
-          <t>45 min</t>
+          <t>Hot or chilled</t>
         </is>
       </c>
       <c r="D6" s="39" t="inlineStr">
         <is>
-          <t>55 min</t>
+          <t>Prep 10 min · Cook 45 min</t>
         </is>
       </c>
     </row>
@@ -3518,29 +4807,169 @@
       <c r="C15" s="45" t="n"/>
       <c r="D15" s="45" t="n"/>
     </row>
-    <row r="16" ht="36" customHeight="1">
+    <row r="16" ht="42" customHeight="1">
       <c r="A16" s="46" t="n">
         <v>1</v>
       </c>
       <c r="B16" s="47" t="inlineStr">
         <is>
-          <t>Simmer. Festival bowl.</t>
+          <t>Mise en place. Rice, milk, sugar, cardamom, nuts. Heavy stainless steel milk pot — never aluminium.</t>
         </is>
       </c>
       <c r="C16" s="48" t="n"/>
       <c r="D16" s="48" t="n"/>
     </row>
+    <row r="17" ht="36" customHeight="1">
+      <c r="A17" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="B17" s="30" t="inlineStr">
+        <is>
+          <t>Simmer rice in milk 35–45 minutes, stirring, until creamy.</t>
+        </is>
+      </c>
+      <c r="C17" s="31" t="n"/>
+      <c r="D17" s="31" t="n"/>
+    </row>
+    <row r="18" ht="36" customHeight="1">
+      <c r="A18" s="46" t="n">
+        <v>3</v>
+      </c>
+      <c r="B18" s="47" t="inlineStr">
+        <is>
+          <t>Add sugar, cardamom and nuts. Cook 5 minutes more.</t>
+        </is>
+      </c>
+      <c r="C18" s="48" t="n"/>
+      <c r="D18" s="48" t="n"/>
+    </row>
+    <row r="19" ht="36" customHeight="1">
+      <c r="A19" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="B19" s="30" t="inlineStr">
+        <is>
+          <t>Doneness: coats a spoon. Serve hot or chilled.</t>
+        </is>
+      </c>
+      <c r="C19" s="31" t="n"/>
+      <c r="D19" s="31" t="n"/>
+    </row>
+    <row r="20" ht="42" customHeight="1">
+      <c r="A20" s="46" t="n">
+        <v>5</v>
+      </c>
+      <c r="B20" s="47" t="inlineStr">
+        <is>
+          <t>Label milk and tree nuts. Festival bowl — hold to the service temperature you choose.</t>
+        </is>
+      </c>
+      <c r="C20" s="48" t="n"/>
+      <c r="D20" s="48" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="21" t="inlineStr">
+        <is>
+          <t>Nutrition per portion</t>
+        </is>
+      </c>
+      <c r="B22" s="22" t="n"/>
+      <c r="C22" s="22" t="n"/>
+      <c r="D22" s="22" t="n"/>
+    </row>
+    <row r="23" ht="36" customHeight="1">
+      <c r="A23" s="12" t="inlineStr">
+        <is>
+          <t>kcal 0  ·  Protein 0 g  ·  Carbs 0 g  ·  Fat 0 g  ·  Fibre 0 g. Nutrition is a kitchen estimate from typical produce values, not a laboratory analysis.</t>
+        </is>
+      </c>
+      <c r="B23" s="49" t="n"/>
+      <c r="C23" s="49" t="n"/>
+      <c r="D23" s="49" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="24" t="inlineStr">
+        <is>
+          <t>Allergens</t>
+        </is>
+      </c>
+      <c r="B24" s="6" t="n"/>
+      <c r="C24" s="6" t="n"/>
+      <c r="D24" s="6" t="n"/>
+    </row>
+    <row r="25" ht="48" customHeight="1">
+      <c r="A25" s="25" t="inlineStr">
+        <is>
+          <t>Milk · Always verify labels; this card is a kitchen estimate, not a lab certificate.</t>
+        </is>
+      </c>
+      <c r="B25" s="26" t="n"/>
+      <c r="C25" s="26" t="n"/>
+      <c r="D25" s="26" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="24" t="inlineStr">
+        <is>
+          <t>Chef notes</t>
+        </is>
+      </c>
+      <c r="B26" s="6" t="n"/>
+      <c r="C26" s="6" t="n"/>
+      <c r="D26" s="6" t="n"/>
+    </row>
+    <row r="27" ht="72" customHeight="1">
+      <c r="A27" s="25" t="inlineStr">
+        <is>
+          <t>For Kheer (rice milk, national): keep the mix slightly drier than you think; wet mixes split or go greasy. Bloom hing in hot fat 20–30 seconds; raw hing tastes medicinal. Commercial hing is often cut with wheat flour — use a gluten-free hing if you must mark Gluten Free. Never cook tomato, tamarind, lemon, yogurt or milk in aluminium; use stainless steel, iron, clay or glass. Spice blends: read the packet. Many garam masalas hide onion or garlic powder.</t>
+        </is>
+      </c>
+      <c r="B27" s="26" t="n"/>
+      <c r="C27" s="26" t="n"/>
+      <c r="D27" s="26" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="50" t="inlineStr">
+        <is>
+          <t>Service notes</t>
+        </is>
+      </c>
+      <c r="B28" s="51" t="n"/>
+      <c r="C28" s="51" t="n"/>
+      <c r="D28" s="51" t="n"/>
+    </row>
+    <row r="29" ht="64" customHeight="1">
+      <c r="A29" s="12" t="inlineStr">
+        <is>
+          <t>Serve in steel or glass bowls. If chilled, take out 5 minutes before the pass. Service temperature: Hot or chilled. Allergen label for this dish: Milk; Always verify labels; this card is a kitchen estimate, not a lab certificate. State clearly: vegetarian, no onion, no garlic, no eggs, no meat, no fish. Nutrition on this card is an estimate for 1 portion of 4.</t>
+        </is>
+      </c>
+      <c r="B29" s="49" t="n"/>
+      <c r="C29" s="49" t="n"/>
+      <c r="D29" s="49" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="22">
+    <mergeCell ref="A23:D23"/>
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="A22:D22"/>
+    <mergeCell ref="B17:D17"/>
+    <mergeCell ref="A29:D29"/>
+    <mergeCell ref="A28:D28"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="B19:D19"/>
+    <mergeCell ref="A24:D24"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B15:D15"/>
+    <mergeCell ref="B20:D20"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="C12:D12"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="A25:D25"/>
+    <mergeCell ref="B16:D16"/>
+    <mergeCell ref="A27:D27"/>
     <mergeCell ref="A3:D3"/>
+    <mergeCell ref="A26:D26"/>
+    <mergeCell ref="B18:D18"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="B15:D15"/>
-    <mergeCell ref="B16:D16"/>
     <mergeCell ref="A14:D14"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3819,7 +5248,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D17"/>
+  <dimension ref="A1:D30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3831,7 +5260,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RECIPE CARD  ·  Rasmalai (Bengal-to-nation)</t>
+          <t>Parslia Kitchen OS · RECIPE CARD · Rasmalai (Bengal-to-nation)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3841,7 +5270,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Pan-India kitchen  ·  Dessert  ·  Dishes cooked in homes all over India</t>
+          <t>Pure Prasad · No onion · No garlic · No eggs · No meat · No fish  ·  Pan-India  ·  Dessert</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -3861,44 +5290,44 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="38" t="inlineStr">
         <is>
-          <t>Serves</t>
+          <t>YIELD</t>
         </is>
       </c>
       <c r="B5" s="38" t="inlineStr">
         <is>
-          <t>Prep</t>
+          <t>PORTION</t>
         </is>
       </c>
       <c r="C5" s="38" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>SERVICE</t>
         </is>
       </c>
       <c r="D5" s="38" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>TIME</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="39" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 portions</t>
         </is>
       </c>
       <c r="B6" s="39" t="inlineStr">
         <is>
-          <t>30 min</t>
+          <t>1 portion</t>
         </is>
       </c>
       <c r="C6" s="39" t="inlineStr">
         <is>
-          <t>40 min</t>
+          <t>Hot</t>
         </is>
       </c>
       <c r="D6" s="39" t="inlineStr">
         <is>
-          <t>70 min</t>
+          <t>Prep 30 min · Cook 40 min</t>
         </is>
       </c>
     </row>
@@ -3992,31 +5421,171 @@
       <c r="C16" s="45" t="n"/>
       <c r="D16" s="45" t="n"/>
     </row>
-    <row r="17" ht="36" customHeight="1">
+    <row r="17" ht="42" customHeight="1">
       <c r="A17" s="46" t="n">
         <v>1</v>
       </c>
       <c r="B17" s="47" t="inlineStr">
         <is>
-          <t>Poach chhena. Soak in rabri.</t>
+          <t>Mise en place. Fresh chhena discs, reduced milk (rabri) with saffron and pistachio. Steel pots — never aluminium.</t>
         </is>
       </c>
       <c r="C17" s="48" t="n"/>
       <c r="D17" s="48" t="n"/>
     </row>
+    <row r="18" ht="42" customHeight="1">
+      <c r="A18" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="B18" s="30" t="inlineStr">
+        <is>
+          <t>Poach chhena discs in light sugar syrup 8–10 minutes until they swell. Squeeze gently.</t>
+        </is>
+      </c>
+      <c r="C18" s="31" t="n"/>
+      <c r="D18" s="31" t="n"/>
+    </row>
+    <row r="19" ht="36" customHeight="1">
+      <c r="A19" s="46" t="n">
+        <v>3</v>
+      </c>
+      <c r="B19" s="47" t="inlineStr">
+        <is>
+          <t>Soak in warm rabri at least 1 hour, chilled after that.</t>
+        </is>
+      </c>
+      <c r="C19" s="48" t="n"/>
+      <c r="D19" s="48" t="n"/>
+    </row>
+    <row r="20" ht="42" customHeight="1">
+      <c r="A20" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="B20" s="30" t="inlineStr">
+        <is>
+          <t>Doneness: discs spongy, milk thick enough to nap, saffron aroma. Serve chilled, 2 discs per portion.</t>
+        </is>
+      </c>
+      <c r="C20" s="31" t="n"/>
+      <c r="D20" s="31" t="n"/>
+    </row>
+    <row r="21" ht="36" customHeight="1">
+      <c r="A21" s="46" t="n">
+        <v>5</v>
+      </c>
+      <c r="B21" s="47" t="inlineStr">
+        <is>
+          <t>Hold refrigerated. Label milk and tree nuts.</t>
+        </is>
+      </c>
+      <c r="C21" s="48" t="n"/>
+      <c r="D21" s="48" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="21" t="inlineStr">
+        <is>
+          <t>Nutrition per portion</t>
+        </is>
+      </c>
+      <c r="B23" s="22" t="n"/>
+      <c r="C23" s="22" t="n"/>
+      <c r="D23" s="22" t="n"/>
+    </row>
+    <row r="24" ht="36" customHeight="1">
+      <c r="A24" s="12" t="inlineStr">
+        <is>
+          <t>kcal 129  ·  Protein 9 g  ·  Carbs 2 g  ·  Fat 10 g  ·  Fibre 0 g. Nutrition is a kitchen estimate from typical produce values, not a laboratory analysis.</t>
+        </is>
+      </c>
+      <c r="B24" s="49" t="n"/>
+      <c r="C24" s="49" t="n"/>
+      <c r="D24" s="49" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="24" t="inlineStr">
+        <is>
+          <t>Allergens</t>
+        </is>
+      </c>
+      <c r="B25" s="6" t="n"/>
+      <c r="C25" s="6" t="n"/>
+      <c r="D25" s="6" t="n"/>
+    </row>
+    <row r="26" ht="48" customHeight="1">
+      <c r="A26" s="25" t="inlineStr">
+        <is>
+          <t>Milk · Tree nuts · Always verify labels; this card is a kitchen estimate, not a lab certificate.</t>
+        </is>
+      </c>
+      <c r="B26" s="26" t="n"/>
+      <c r="C26" s="26" t="n"/>
+      <c r="D26" s="26" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="24" t="inlineStr">
+        <is>
+          <t>Chef notes</t>
+        </is>
+      </c>
+      <c r="B27" s="6" t="n"/>
+      <c r="C27" s="6" t="n"/>
+      <c r="D27" s="6" t="n"/>
+    </row>
+    <row r="28" ht="72" customHeight="1">
+      <c r="A28" s="25" t="inlineStr">
+        <is>
+          <t>For Rasmalai (Bengal-to-nation): keep the mix slightly drier than you think; wet mixes split or go greasy. Bloom hing in hot fat 20–30 seconds; raw hing tastes medicinal. Commercial hing is often cut with wheat flour — use a gluten-free hing if you must mark Gluten Free. Never cook tomato, tamarind, lemon, yogurt or milk in aluminium; use stainless steel, iron, clay or glass. Spice blends: read the packet. Many garam masalas hide onion or garlic powder.</t>
+        </is>
+      </c>
+      <c r="B28" s="26" t="n"/>
+      <c r="C28" s="26" t="n"/>
+      <c r="D28" s="26" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="50" t="inlineStr">
+        <is>
+          <t>Service notes</t>
+        </is>
+      </c>
+      <c r="B29" s="51" t="n"/>
+      <c r="C29" s="51" t="n"/>
+      <c r="D29" s="51" t="n"/>
+    </row>
+    <row r="30" ht="64" customHeight="1">
+      <c r="A30" s="12" t="inlineStr">
+        <is>
+          <t>Serve in steel or glass bowls. If chilled, take out 5 minutes before the pass. Service temperature: Hot. Allergen label for this dish: Milk; Tree nuts; Always verify labels; this card is a kitchen estimate, not a lab certificate. State clearly: vegetarian, no onion, no garlic, no eggs, no meat, no fish. Nutrition on this card is an estimate for 1 portion of 4.</t>
+        </is>
+      </c>
+      <c r="B30" s="49" t="n"/>
+      <c r="C30" s="49" t="n"/>
+      <c r="D30" s="49" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="11">
+  <mergeCells count="23">
+    <mergeCell ref="A23:D23"/>
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="B17:D17"/>
+    <mergeCell ref="A29:D29"/>
+    <mergeCell ref="A28:D28"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="B19:D19"/>
+    <mergeCell ref="A30:D30"/>
+    <mergeCell ref="A15:D15"/>
+    <mergeCell ref="A24:D24"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B20:D20"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="C12:D12"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="A25:D25"/>
+    <mergeCell ref="B16:D16"/>
+    <mergeCell ref="A27:D27"/>
     <mergeCell ref="A3:D3"/>
-    <mergeCell ref="B17:D17"/>
-    <mergeCell ref="A15:D15"/>
+    <mergeCell ref="A26:D26"/>
+    <mergeCell ref="B18:D18"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="B16:D16"/>
+    <mergeCell ref="B21:D21"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -4030,7 +5599,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D17"/>
+  <dimension ref="A1:D30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -4042,7 +5611,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RECIPE CARD  ·  Fruit custard (party, veg cornstarch)</t>
+          <t>Parslia Kitchen OS · RECIPE CARD · Fruit custard (party, veg cornstarch)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4052,7 +5621,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Pan-India kitchen  ·  Dessert  ·  Dishes cooked in homes all over India</t>
+          <t>Pure Prasad · No onion · No garlic · No eggs · No meat · No fish  ·  Pan-India  ·  Dessert</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -4072,44 +5641,44 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="38" t="inlineStr">
         <is>
-          <t>Serves</t>
+          <t>YIELD</t>
         </is>
       </c>
       <c r="B5" s="38" t="inlineStr">
         <is>
-          <t>Prep</t>
+          <t>PORTION</t>
         </is>
       </c>
       <c r="C5" s="38" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>SERVICE</t>
         </is>
       </c>
       <c r="D5" s="38" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>TIME</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="39" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 portions</t>
         </is>
       </c>
       <c r="B6" s="39" t="inlineStr">
         <is>
-          <t>20 min</t>
+          <t>1 portion</t>
         </is>
       </c>
       <c r="C6" s="39" t="inlineStr">
         <is>
-          <t>15 min</t>
+          <t>Hot or chilled</t>
         </is>
       </c>
       <c r="D6" s="39" t="inlineStr">
         <is>
-          <t>35 min</t>
+          <t>Prep 20 min · Cook 15 min</t>
         </is>
       </c>
     </row>
@@ -4203,31 +5772,171 @@
       <c r="C16" s="45" t="n"/>
       <c r="D16" s="45" t="n"/>
     </row>
-    <row r="17" ht="36" customHeight="1">
+    <row r="17" ht="42" customHeight="1">
       <c r="A17" s="46" t="n">
         <v>1</v>
       </c>
       <c r="B17" s="47" t="inlineStr">
         <is>
-          <t>Cook custard. Chill. Fold fruit. No egg.</t>
+          <t>Mise en place. Milk, sugar, cornstarch, mixed fruit, cardamom. Steel pot then a glass bowl. No eggs.</t>
         </is>
       </c>
       <c r="C17" s="48" t="n"/>
       <c r="D17" s="48" t="n"/>
     </row>
+    <row r="18" ht="54" customHeight="1">
+      <c r="A18" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="B18" s="30" t="inlineStr">
+        <is>
+          <t>Cook milk, sugar and slurried cornstarch on medium, stirring, until it thickens and the raw starch taste is gone, 6–8 minutes. Add cardamom. Cool completely, stirring so a skin does not form.</t>
+        </is>
+      </c>
+      <c r="C18" s="31" t="n"/>
+      <c r="D18" s="31" t="n"/>
+    </row>
+    <row r="19" ht="42" customHeight="1">
+      <c r="A19" s="46" t="n">
+        <v>3</v>
+      </c>
+      <c r="B19" s="47" t="inlineStr">
+        <is>
+          <t>Fold diced fruit only when the custard is cold — warm custard weeps and the fruit goes dull.</t>
+        </is>
+      </c>
+      <c r="C19" s="48" t="n"/>
+      <c r="D19" s="48" t="n"/>
+    </row>
+    <row r="20" ht="36" customHeight="1">
+      <c r="A20" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="B20" s="30" t="inlineStr">
+        <is>
+          <t>Doneness: spoonable, fruit distinct, no egg. Chill 1 hour.</t>
+        </is>
+      </c>
+      <c r="C20" s="31" t="n"/>
+      <c r="D20" s="31" t="n"/>
+    </row>
+    <row r="21" ht="42" customHeight="1">
+      <c r="A21" s="46" t="n">
+        <v>5</v>
+      </c>
+      <c r="B21" s="47" t="inlineStr">
+        <is>
+          <t>Serve cold. Hold 4 hours chilled. Label milk. Use fruit that does not brown badly, or toss banana at the last minute.</t>
+        </is>
+      </c>
+      <c r="C21" s="48" t="n"/>
+      <c r="D21" s="48" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="21" t="inlineStr">
+        <is>
+          <t>Nutrition per portion</t>
+        </is>
+      </c>
+      <c r="B23" s="22" t="n"/>
+      <c r="C23" s="22" t="n"/>
+      <c r="D23" s="22" t="n"/>
+    </row>
+    <row r="24" ht="36" customHeight="1">
+      <c r="A24" s="12" t="inlineStr">
+        <is>
+          <t>kcal 160  ·  Protein 8 g  ·  Carbs 12 g  ·  Fat 9 g  ·  Fibre 0 g. Nutrition is a kitchen estimate from typical produce values, not a laboratory analysis.</t>
+        </is>
+      </c>
+      <c r="B24" s="49" t="n"/>
+      <c r="C24" s="49" t="n"/>
+      <c r="D24" s="49" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="24" t="inlineStr">
+        <is>
+          <t>Allergens</t>
+        </is>
+      </c>
+      <c r="B25" s="6" t="n"/>
+      <c r="C25" s="6" t="n"/>
+      <c r="D25" s="6" t="n"/>
+    </row>
+    <row r="26" ht="48" customHeight="1">
+      <c r="A26" s="25" t="inlineStr">
+        <is>
+          <t>Milk · Always verify labels; this card is a kitchen estimate, not a lab certificate.</t>
+        </is>
+      </c>
+      <c r="B26" s="26" t="n"/>
+      <c r="C26" s="26" t="n"/>
+      <c r="D26" s="26" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="24" t="inlineStr">
+        <is>
+          <t>Chef notes</t>
+        </is>
+      </c>
+      <c r="B27" s="6" t="n"/>
+      <c r="C27" s="6" t="n"/>
+      <c r="D27" s="6" t="n"/>
+    </row>
+    <row r="28" ht="72" customHeight="1">
+      <c r="A28" s="25" t="inlineStr">
+        <is>
+          <t>For Fruit custard (party, veg cornstarch): keep the mix slightly drier than you think; wet mixes split or go greasy. Bloom hing in hot fat 20–30 seconds; raw hing tastes medicinal. Commercial hing is often cut with wheat flour — use a gluten-free hing if you must mark Gluten Free. Never cook tomato, tamarind, lemon, yogurt or milk in aluminium; use stainless steel, iron, clay or glass. Spice blends: read the packet. Many garam masalas hide onion or garlic powder.</t>
+        </is>
+      </c>
+      <c r="B28" s="26" t="n"/>
+      <c r="C28" s="26" t="n"/>
+      <c r="D28" s="26" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="50" t="inlineStr">
+        <is>
+          <t>Service notes</t>
+        </is>
+      </c>
+      <c r="B29" s="51" t="n"/>
+      <c r="C29" s="51" t="n"/>
+      <c r="D29" s="51" t="n"/>
+    </row>
+    <row r="30" ht="64" customHeight="1">
+      <c r="A30" s="12" t="inlineStr">
+        <is>
+          <t>Serve in steel or glass bowls. If chilled, take out 5 minutes before the pass. Service temperature: Hot or chilled. Allergen label for this dish: Milk; Always verify labels; this card is a kitchen estimate, not a lab certificate. State clearly: vegetarian, no onion, no garlic, no eggs, no meat, no fish. Nutrition on this card is an estimate for 1 portion of 4.</t>
+        </is>
+      </c>
+      <c r="B30" s="49" t="n"/>
+      <c r="C30" s="49" t="n"/>
+      <c r="D30" s="49" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="11">
+  <mergeCells count="23">
+    <mergeCell ref="A23:D23"/>
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="B17:D17"/>
+    <mergeCell ref="A29:D29"/>
+    <mergeCell ref="A28:D28"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="B19:D19"/>
+    <mergeCell ref="A30:D30"/>
+    <mergeCell ref="A15:D15"/>
+    <mergeCell ref="A24:D24"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B20:D20"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="C12:D12"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="A25:D25"/>
+    <mergeCell ref="B16:D16"/>
+    <mergeCell ref="A27:D27"/>
     <mergeCell ref="A3:D3"/>
-    <mergeCell ref="B17:D17"/>
-    <mergeCell ref="A15:D15"/>
+    <mergeCell ref="A26:D26"/>
+    <mergeCell ref="B18:D18"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="B16:D16"/>
+    <mergeCell ref="B21:D21"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -4241,7 +5950,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D23"/>
+  <dimension ref="A1:D36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -4253,7 +5962,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RECIPE CARD  ·  Kachumber no onion (national)</t>
+          <t>Parslia Kitchen OS · RECIPE CARD · Kachumber no onion (national)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4263,7 +5972,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Pan-India kitchen  ·  Salad  ·  Dishes cooked in homes all over India</t>
+          <t>Pure Prasad · No onion · No garlic · No eggs · No meat · No fish  ·  Pan-India  ·  Salad</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -4283,44 +5992,44 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="38" t="inlineStr">
         <is>
-          <t>Serves</t>
+          <t>YIELD</t>
         </is>
       </c>
       <c r="B5" s="38" t="inlineStr">
         <is>
-          <t>Prep</t>
+          <t>PORTION</t>
         </is>
       </c>
       <c r="C5" s="38" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>SERVICE</t>
         </is>
       </c>
       <c r="D5" s="38" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>TIME</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="39" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 portions</t>
         </is>
       </c>
       <c r="B6" s="39" t="inlineStr">
         <is>
-          <t>10 min</t>
+          <t>1 portion</t>
         </is>
       </c>
       <c r="C6" s="39" t="inlineStr">
         <is>
-          <t>0 min</t>
+          <t>Cold</t>
         </is>
       </c>
       <c r="D6" s="39" t="inlineStr">
         <is>
-          <t>10 min</t>
+          <t>Prep 10 min · Cook 0 min</t>
         </is>
       </c>
     </row>
@@ -4522,37 +6231,177 @@
       <c r="C22" s="45" t="n"/>
       <c r="D22" s="45" t="n"/>
     </row>
-    <row r="23" ht="36" customHeight="1">
+    <row r="23" ht="42" customHeight="1">
       <c r="A23" s="46" t="n">
         <v>1</v>
       </c>
       <c r="B23" s="47" t="inlineStr">
         <is>
-          <t>Chop. Toss.</t>
+          <t>Mise en place. Dice cucumber, tomato and chilli even. Steel or glass bowl. No onion.</t>
         </is>
       </c>
       <c r="C23" s="48" t="n"/>
       <c r="D23" s="48" t="n"/>
     </row>
+    <row r="24" ht="36" customHeight="1">
+      <c r="A24" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="B24" s="30" t="inlineStr">
+        <is>
+          <t>Toss with lemon, cumin, coriander and salt just before service.</t>
+        </is>
+      </c>
+      <c r="C24" s="31" t="n"/>
+      <c r="D24" s="31" t="n"/>
+    </row>
+    <row r="25" ht="36" customHeight="1">
+      <c r="A25" s="46" t="n">
+        <v>3</v>
+      </c>
+      <c r="B25" s="47" t="inlineStr">
+        <is>
+          <t>Doneness: crisp, bright, not watery. Taste salt and lemon.</t>
+        </is>
+      </c>
+      <c r="C25" s="48" t="n"/>
+      <c r="D25" s="48" t="n"/>
+    </row>
+    <row r="26" ht="36" customHeight="1">
+      <c r="A26" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="B26" s="30" t="inlineStr">
+        <is>
+          <t>Serve cold as a side salad.</t>
+        </is>
+      </c>
+      <c r="C26" s="31" t="n"/>
+      <c r="D26" s="31" t="n"/>
+    </row>
+    <row r="27" ht="36" customHeight="1">
+      <c r="A27" s="46" t="n">
+        <v>5</v>
+      </c>
+      <c r="B27" s="47" t="inlineStr">
+        <is>
+          <t>Hold 20 minutes. Drain if it weeps. Do not add onion at the pass.</t>
+        </is>
+      </c>
+      <c r="C27" s="48" t="n"/>
+      <c r="D27" s="48" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="21" t="inlineStr">
+        <is>
+          <t>Nutrition per portion</t>
+        </is>
+      </c>
+      <c r="B29" s="22" t="n"/>
+      <c r="C29" s="22" t="n"/>
+      <c r="D29" s="22" t="n"/>
+    </row>
+    <row r="30" ht="36" customHeight="1">
+      <c r="A30" s="12" t="inlineStr">
+        <is>
+          <t>kcal 30  ·  Protein 1 g  ·  Carbs 7 g  ·  Fat 0 g  ·  Fibre 1 g. Nutrition is a kitchen estimate from typical produce values, not a laboratory analysis.</t>
+        </is>
+      </c>
+      <c r="B30" s="49" t="n"/>
+      <c r="C30" s="49" t="n"/>
+      <c r="D30" s="49" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="24" t="inlineStr">
+        <is>
+          <t>Allergens</t>
+        </is>
+      </c>
+      <c r="B31" s="6" t="n"/>
+      <c r="C31" s="6" t="n"/>
+      <c r="D31" s="6" t="n"/>
+    </row>
+    <row r="32" ht="48" customHeight="1">
+      <c r="A32" s="25" t="inlineStr">
+        <is>
+          <t>None identified in this spec — still verify hing brand (many contain wheat) and spice blends.</t>
+        </is>
+      </c>
+      <c r="B32" s="26" t="n"/>
+      <c r="C32" s="26" t="n"/>
+      <c r="D32" s="26" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="24" t="inlineStr">
+        <is>
+          <t>Chef notes</t>
+        </is>
+      </c>
+      <c r="B33" s="6" t="n"/>
+      <c r="C33" s="6" t="n"/>
+      <c r="D33" s="6" t="n"/>
+    </row>
+    <row r="34" ht="72" customHeight="1">
+      <c r="A34" s="25" t="inlineStr">
+        <is>
+          <t>For Kachumber no onion (national): squeeze wet vegetables dry or the bowl weeps on the pass. Season slightly higher than you think — cold dulls salt. No onion, no garlic, no allium garnish. Use steel or glass, never aluminium. Dress at the last minute. Verify dahi and spice labels.</t>
+        </is>
+      </c>
+      <c r="B34" s="26" t="n"/>
+      <c r="C34" s="26" t="n"/>
+      <c r="D34" s="26" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="50" t="inlineStr">
+        <is>
+          <t>Service notes</t>
+        </is>
+      </c>
+      <c r="B35" s="51" t="n"/>
+      <c r="C35" s="51" t="n"/>
+      <c r="D35" s="51" t="n"/>
+    </row>
+    <row r="36" ht="64" customHeight="1">
+      <c r="A36" s="12" t="inlineStr">
+        <is>
+          <t>Dress at the last minute. Toss at the pass, do not send a wet bowl. Service temperature: Cold. Allergen label for this dish: None identified in this spec — still verify hing brand (many contain wheat) and spice blends. State clearly: vegetarian, no onion, no garlic, no eggs, no meat, no fish. Nutrition on this card is an estimate for 1 portion of 4.</t>
+        </is>
+      </c>
+      <c r="B36" s="49" t="n"/>
+      <c r="C36" s="49" t="n"/>
+      <c r="D36" s="49" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="17">
+  <mergeCells count="29">
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="A35:D35"/>
+    <mergeCell ref="A29:D29"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="A34:D34"/>
+    <mergeCell ref="A30:D30"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="A36:D36"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="C12:D12"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="C17:D17"/>
     <mergeCell ref="B22:D22"/>
     <mergeCell ref="A3:D3"/>
     <mergeCell ref="C19:D19"/>
     <mergeCell ref="A21:D21"/>
-    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="B27:D27"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="C17:D17"/>
     <mergeCell ref="C18:D18"/>
+    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="A32:D32"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -4566,7 +6415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D17"/>
+  <dimension ref="A1:D30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -4578,7 +6427,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RECIPE CARD  ·  Dahi raita mixed veg (no onion)</t>
+          <t>Parslia Kitchen OS · RECIPE CARD · Dahi raita mixed veg (no onion)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4588,7 +6437,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Pan-India kitchen  ·  Salad  ·  Dishes cooked in homes all over India</t>
+          <t>Pure Prasad · No onion · No garlic · No eggs · No meat · No fish  ·  Pan-India  ·  Salad</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -4608,44 +6457,44 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="38" t="inlineStr">
         <is>
-          <t>Serves</t>
+          <t>YIELD</t>
         </is>
       </c>
       <c r="B5" s="38" t="inlineStr">
         <is>
-          <t>Prep</t>
+          <t>PORTION</t>
         </is>
       </c>
       <c r="C5" s="38" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>SERVICE</t>
         </is>
       </c>
       <c r="D5" s="38" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>TIME</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="39" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 portions</t>
         </is>
       </c>
       <c r="B6" s="39" t="inlineStr">
         <is>
-          <t>10 min</t>
+          <t>1 portion</t>
         </is>
       </c>
       <c r="C6" s="39" t="inlineStr">
         <is>
-          <t>0 min</t>
+          <t>Cold</t>
         </is>
       </c>
       <c r="D6" s="39" t="inlineStr">
         <is>
-          <t>10 min</t>
+          <t>Prep 10 min · Cook 0 min</t>
         </is>
       </c>
     </row>
@@ -4739,31 +6588,171 @@
       <c r="C16" s="45" t="n"/>
       <c r="D16" s="45" t="n"/>
     </row>
-    <row r="17" ht="36" customHeight="1">
+    <row r="17" ht="42" customHeight="1">
       <c r="A17" s="46" t="n">
         <v>1</v>
       </c>
       <c r="B17" s="47" t="inlineStr">
         <is>
-          <t>Mix. Chill.</t>
+          <t>Mise en place. Whisk dahi smooth. Small dice cucumber and boiled potato. No onion.</t>
         </is>
       </c>
       <c r="C17" s="48" t="n"/>
       <c r="D17" s="48" t="n"/>
     </row>
+    <row r="18" ht="42" customHeight="1">
+      <c r="A18" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="B18" s="30" t="inlineStr">
+        <is>
+          <t>Fold vegetables with cumin, salt, chilli powder and coriander. Chill 15 minutes. Stir.</t>
+        </is>
+      </c>
+      <c r="C18" s="31" t="n"/>
+      <c r="D18" s="31" t="n"/>
+    </row>
+    <row r="19" ht="36" customHeight="1">
+      <c r="A19" s="46" t="n">
+        <v>3</v>
+      </c>
+      <c r="B19" s="47" t="inlineStr">
+        <is>
+          <t>Doneness: thick, seasoned, vegetables distinct. Serve cold.</t>
+        </is>
+      </c>
+      <c r="C19" s="48" t="n"/>
+      <c r="D19" s="48" t="n"/>
+    </row>
+    <row r="20" ht="36" customHeight="1">
+      <c r="A20" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="B20" s="30" t="inlineStr">
+        <is>
+          <t>Hold 2 hours chilled. Stir at the pass.</t>
+        </is>
+      </c>
+      <c r="C20" s="31" t="n"/>
+      <c r="D20" s="31" t="n"/>
+    </row>
+    <row r="21" ht="42" customHeight="1">
+      <c r="A21" s="46" t="n">
+        <v>5</v>
+      </c>
+      <c r="B21" s="47" t="inlineStr">
+        <is>
+          <t>Label milk. Keep onion off this bowl even if the rest of the table has kachumber with onion.</t>
+        </is>
+      </c>
+      <c r="C21" s="48" t="n"/>
+      <c r="D21" s="48" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="21" t="inlineStr">
+        <is>
+          <t>Nutrition per portion</t>
+        </is>
+      </c>
+      <c r="B23" s="22" t="n"/>
+      <c r="C23" s="22" t="n"/>
+      <c r="D23" s="22" t="n"/>
+    </row>
+    <row r="24" ht="36" customHeight="1">
+      <c r="A24" s="12" t="inlineStr">
+        <is>
+          <t>kcal 61  ·  Protein 4 g  ·  Carbs 5 g  ·  Fat 3 g  ·  Fibre 0 g. Nutrition is a kitchen estimate from typical produce values, not a laboratory analysis.</t>
+        </is>
+      </c>
+      <c r="B24" s="49" t="n"/>
+      <c r="C24" s="49" t="n"/>
+      <c r="D24" s="49" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="24" t="inlineStr">
+        <is>
+          <t>Allergens</t>
+        </is>
+      </c>
+      <c r="B25" s="6" t="n"/>
+      <c r="C25" s="6" t="n"/>
+      <c r="D25" s="6" t="n"/>
+    </row>
+    <row r="26" ht="48" customHeight="1">
+      <c r="A26" s="25" t="inlineStr">
+        <is>
+          <t>Milk · Always verify labels; this card is a kitchen estimate, not a lab certificate.</t>
+        </is>
+      </c>
+      <c r="B26" s="26" t="n"/>
+      <c r="C26" s="26" t="n"/>
+      <c r="D26" s="26" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="24" t="inlineStr">
+        <is>
+          <t>Chef notes</t>
+        </is>
+      </c>
+      <c r="B27" s="6" t="n"/>
+      <c r="C27" s="6" t="n"/>
+      <c r="D27" s="6" t="n"/>
+    </row>
+    <row r="28" ht="72" customHeight="1">
+      <c r="A28" s="25" t="inlineStr">
+        <is>
+          <t>For Dahi raita mixed veg (no onion): squeeze wet vegetables dry or the bowl weeps on the pass. Season slightly higher than you think — cold dulls salt. No onion, no garlic, no allium garnish. Use steel or glass, never aluminium. Dress at the last minute. Verify dahi and spice labels.</t>
+        </is>
+      </c>
+      <c r="B28" s="26" t="n"/>
+      <c r="C28" s="26" t="n"/>
+      <c r="D28" s="26" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="50" t="inlineStr">
+        <is>
+          <t>Service notes</t>
+        </is>
+      </c>
+      <c r="B29" s="51" t="n"/>
+      <c r="C29" s="51" t="n"/>
+      <c r="D29" s="51" t="n"/>
+    </row>
+    <row r="30" ht="64" customHeight="1">
+      <c r="A30" s="12" t="inlineStr">
+        <is>
+          <t>Serve in a steel or glass bowl. Stir at the pass so it is not split or settled. Service temperature: Cold. Allergen label for this dish: Milk; Always verify labels; this card is a kitchen estimate, not a lab certificate. State clearly: vegetarian, no onion, no garlic, no eggs, no meat, no fish. Nutrition on this card is an estimate for 1 portion of 4.</t>
+        </is>
+      </c>
+      <c r="B30" s="49" t="n"/>
+      <c r="C30" s="49" t="n"/>
+      <c r="D30" s="49" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="11">
+  <mergeCells count="23">
+    <mergeCell ref="A23:D23"/>
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="B17:D17"/>
+    <mergeCell ref="A29:D29"/>
+    <mergeCell ref="A28:D28"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="B19:D19"/>
+    <mergeCell ref="A30:D30"/>
+    <mergeCell ref="A15:D15"/>
+    <mergeCell ref="A24:D24"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B20:D20"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="C12:D12"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="A25:D25"/>
+    <mergeCell ref="B16:D16"/>
+    <mergeCell ref="A27:D27"/>
     <mergeCell ref="A3:D3"/>
-    <mergeCell ref="B17:D17"/>
-    <mergeCell ref="A15:D15"/>
+    <mergeCell ref="A26:D26"/>
+    <mergeCell ref="B18:D18"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="B16:D16"/>
+    <mergeCell ref="B21:D21"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -4777,7 +6766,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D17"/>
+  <dimension ref="A1:D30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -4789,7 +6778,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RECIPE CARD  ·  Sprouts chaat (no onion)</t>
+          <t>Parslia Kitchen OS · RECIPE CARD · Sprouts chaat (no onion)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4799,7 +6788,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Pan-India kitchen  ·  Salad  ·  Dishes cooked in homes all over India</t>
+          <t>Pure Prasad · No onion · No garlic · No eggs · No meat · No fish  ·  Pan-India  ·  Salad</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -4819,44 +6808,44 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="38" t="inlineStr">
         <is>
-          <t>Serves</t>
+          <t>YIELD</t>
         </is>
       </c>
       <c r="B5" s="38" t="inlineStr">
         <is>
-          <t>Prep</t>
+          <t>PORTION</t>
         </is>
       </c>
       <c r="C5" s="38" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>SERVICE</t>
         </is>
       </c>
       <c r="D5" s="38" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>TIME</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="39" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 portions</t>
         </is>
       </c>
       <c r="B6" s="39" t="inlineStr">
         <is>
-          <t>15 min</t>
+          <t>1 portion</t>
         </is>
       </c>
       <c r="C6" s="39" t="inlineStr">
         <is>
-          <t>0 min</t>
+          <t>Cold</t>
         </is>
       </c>
       <c r="D6" s="39" t="inlineStr">
         <is>
-          <t>15 min</t>
+          <t>Prep 15 min · Cook 0 min</t>
         </is>
       </c>
     </row>
@@ -4950,31 +6939,171 @@
       <c r="C16" s="45" t="n"/>
       <c r="D16" s="45" t="n"/>
     </row>
-    <row r="17" ht="36" customHeight="1">
+    <row r="17" ht="42" customHeight="1">
       <c r="A17" s="46" t="n">
         <v>1</v>
       </c>
       <c r="B17" s="47" t="inlineStr">
         <is>
-          <t>Toss. Street-style sattvic.</t>
+          <t>Mise en place. Drain moong sprouts well. Dice tomato. Have lemon, chilli, cumin, sev, coriander, salt and pomegranate ready. No onion.</t>
         </is>
       </c>
       <c r="C17" s="48" t="n"/>
       <c r="D17" s="48" t="n"/>
     </row>
+    <row r="18" ht="42" customHeight="1">
+      <c r="A18" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="B18" s="30" t="inlineStr">
+        <is>
+          <t>Toss sprouts with tomato, lemon, chilli, cumin and salt. Fold sev and pomegranate at the last minute so sev stays crisp.</t>
+        </is>
+      </c>
+      <c r="C18" s="31" t="n"/>
+      <c r="D18" s="31" t="n"/>
+    </row>
+    <row r="19" ht="36" customHeight="1">
+      <c r="A19" s="46" t="n">
+        <v>3</v>
+      </c>
+      <c r="B19" s="47" t="inlineStr">
+        <is>
+          <t>Doneness: tangy, crunchy, not wet. Serve immediately.</t>
+        </is>
+      </c>
+      <c r="C19" s="48" t="n"/>
+      <c r="D19" s="48" t="n"/>
+    </row>
+    <row r="20" ht="36" customHeight="1">
+      <c r="A20" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="B20" s="30" t="inlineStr">
+        <is>
+          <t>Hold 15 minutes only or the sev softens.</t>
+        </is>
+      </c>
+      <c r="C20" s="31" t="n"/>
+      <c r="D20" s="31" t="n"/>
+    </row>
+    <row r="21" ht="36" customHeight="1">
+      <c r="A21" s="46" t="n">
+        <v>5</v>
+      </c>
+      <c r="B21" s="47" t="inlineStr">
+        <is>
+          <t>Street-style sattvic. Label legumes and possible gluten in sev.</t>
+        </is>
+      </c>
+      <c r="C21" s="48" t="n"/>
+      <c r="D21" s="48" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="21" t="inlineStr">
+        <is>
+          <t>Nutrition per portion</t>
+        </is>
+      </c>
+      <c r="B23" s="22" t="n"/>
+      <c r="C23" s="22" t="n"/>
+      <c r="D23" s="22" t="n"/>
+    </row>
+    <row r="24" ht="36" customHeight="1">
+      <c r="A24" s="12" t="inlineStr">
+        <is>
+          <t>kcal 174  ·  Protein 12 g  ·  Carbs 32 g  ·  Fat 1 g  ·  Fibre 8 g. Nutrition is a kitchen estimate from typical produce values, not a laboratory analysis.</t>
+        </is>
+      </c>
+      <c r="B24" s="49" t="n"/>
+      <c r="C24" s="49" t="n"/>
+      <c r="D24" s="49" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="24" t="inlineStr">
+        <is>
+          <t>Allergens</t>
+        </is>
+      </c>
+      <c r="B25" s="6" t="n"/>
+      <c r="C25" s="6" t="n"/>
+      <c r="D25" s="6" t="n"/>
+    </row>
+    <row r="26" ht="48" customHeight="1">
+      <c r="A26" s="25" t="inlineStr">
+        <is>
+          <t>None identified in this spec — still verify hing brand (many contain wheat) and spice blends.</t>
+        </is>
+      </c>
+      <c r="B26" s="26" t="n"/>
+      <c r="C26" s="26" t="n"/>
+      <c r="D26" s="26" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="24" t="inlineStr">
+        <is>
+          <t>Chef notes</t>
+        </is>
+      </c>
+      <c r="B27" s="6" t="n"/>
+      <c r="C27" s="6" t="n"/>
+      <c r="D27" s="6" t="n"/>
+    </row>
+    <row r="28" ht="72" customHeight="1">
+      <c r="A28" s="25" t="inlineStr">
+        <is>
+          <t>For Sprouts chaat (no onion): squeeze wet vegetables dry or the bowl weeps on the pass. Season slightly higher than you think — cold dulls salt. No onion, no garlic, no allium garnish. Use steel or glass, never aluminium. Dress at the last minute. Verify dahi and spice labels.</t>
+        </is>
+      </c>
+      <c r="B28" s="26" t="n"/>
+      <c r="C28" s="26" t="n"/>
+      <c r="D28" s="26" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="50" t="inlineStr">
+        <is>
+          <t>Service notes</t>
+        </is>
+      </c>
+      <c r="B29" s="51" t="n"/>
+      <c r="C29" s="51" t="n"/>
+      <c r="D29" s="51" t="n"/>
+    </row>
+    <row r="30" ht="64" customHeight="1">
+      <c r="A30" s="12" t="inlineStr">
+        <is>
+          <t>Dress at the last minute. Toss at the pass, do not send a wet bowl. Service temperature: Cold. Allergen label for this dish: None identified in this spec — still verify hing brand (many contain wheat) and spice blends. State clearly: vegetarian, no onion, no garlic, no eggs, no meat, no fish. Nutrition on this card is an estimate for 1 portion of 4.</t>
+        </is>
+      </c>
+      <c r="B30" s="49" t="n"/>
+      <c r="C30" s="49" t="n"/>
+      <c r="D30" s="49" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="11">
+  <mergeCells count="23">
+    <mergeCell ref="A23:D23"/>
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="B17:D17"/>
+    <mergeCell ref="A29:D29"/>
+    <mergeCell ref="A28:D28"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="B19:D19"/>
+    <mergeCell ref="A30:D30"/>
+    <mergeCell ref="A15:D15"/>
+    <mergeCell ref="A24:D24"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B20:D20"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="C12:D12"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="A25:D25"/>
+    <mergeCell ref="B16:D16"/>
+    <mergeCell ref="A27:D27"/>
     <mergeCell ref="A3:D3"/>
-    <mergeCell ref="B17:D17"/>
-    <mergeCell ref="A15:D15"/>
+    <mergeCell ref="A26:D26"/>
+    <mergeCell ref="B18:D18"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="B16:D16"/>
+    <mergeCell ref="B21:D21"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -5810,7 +7939,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D16"/>
+  <dimension ref="A1:D30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -5822,7 +7951,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RECIPE CARD  ·  Samosa (nationwide aloo, no onion)</t>
+          <t>Parslia Kitchen OS · RECIPE CARD · Samosa (nationwide aloo, no onion)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5832,7 +7961,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Pan-India kitchen  ·  Starter  ·  Dishes cooked in homes all over India</t>
+          <t>Pure Prasad · No onion · No garlic · No eggs · No meat · No fish  ·  Pan-India  ·  Starter</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -5852,44 +7981,44 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="38" t="inlineStr">
         <is>
-          <t>Serves</t>
+          <t>YIELD</t>
         </is>
       </c>
       <c r="B5" s="38" t="inlineStr">
         <is>
-          <t>Prep</t>
+          <t>PORTION</t>
         </is>
       </c>
       <c r="C5" s="38" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>SERVICE</t>
         </is>
       </c>
       <c r="D5" s="38" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>TIME</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="39" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 portions</t>
         </is>
       </c>
       <c r="B6" s="39" t="inlineStr">
         <is>
-          <t>40 min</t>
+          <t>1 portion</t>
         </is>
       </c>
       <c r="C6" s="39" t="inlineStr">
         <is>
-          <t>25 min</t>
+          <t>Hot</t>
         </is>
       </c>
       <c r="D6" s="39" t="inlineStr">
         <is>
-          <t>65 min</t>
+          <t>Prep 40 min · Cook 25 min</t>
         </is>
       </c>
     </row>
@@ -5965,29 +8094,182 @@
       <c r="C15" s="45" t="n"/>
       <c r="D15" s="45" t="n"/>
     </row>
-    <row r="16" ht="36" customHeight="1">
+    <row r="16" ht="54" customHeight="1">
       <c r="A16" s="46" t="n">
         <v>1</v>
       </c>
       <c r="B16" s="47" t="inlineStr">
         <is>
-          <t>Stuff. Fry. Imli chutney.</t>
+          <t>Mise en place. Prepare a firm maida pastry with ghee and ajwain, and a dry potato-pea filling with cumin, hing and amchur. Steel kadhai for frying — never aluminium. Confirm no onion in the filling.</t>
         </is>
       </c>
       <c r="C16" s="48" t="n"/>
       <c r="D16" s="48" t="n"/>
     </row>
+    <row r="17" ht="42" customHeight="1">
+      <c r="A17" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="B17" s="30" t="inlineStr">
+        <is>
+          <t>Rest dough 20 minutes. Cool the filling completely or the pastry splits.</t>
+        </is>
+      </c>
+      <c r="C17" s="31" t="n"/>
+      <c r="D17" s="31" t="n"/>
+    </row>
+    <row r="18" ht="36" customHeight="1">
+      <c r="A18" s="46" t="n">
+        <v>3</v>
+      </c>
+      <c r="B18" s="47" t="inlineStr">
+        <is>
+          <t>Form cones, fill 2 tbsp, seal with water. No gaps.</t>
+        </is>
+      </c>
+      <c r="C18" s="48" t="n"/>
+      <c r="D18" s="48" t="n"/>
+    </row>
+    <row r="19" ht="42" customHeight="1">
+      <c r="A19" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="B19" s="30" t="inlineStr">
+        <is>
+          <t>Fry at 170–175 C in batches until deep gold, 8–10 minutes. Drain on a steel rack.</t>
+        </is>
+      </c>
+      <c r="C19" s="31" t="n"/>
+      <c r="D19" s="31" t="n"/>
+    </row>
+    <row r="20" ht="36" customHeight="1">
+      <c r="A20" s="46" t="n">
+        <v>5</v>
+      </c>
+      <c r="B20" s="47" t="inlineStr">
+        <is>
+          <t>Doneness: blistered pastry, steaming filling, not greasy.</t>
+        </is>
+      </c>
+      <c r="C20" s="48" t="n"/>
+      <c r="D20" s="48" t="n"/>
+    </row>
+    <row r="21" ht="36" customHeight="1">
+      <c r="A21" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="B21" s="30" t="inlineStr">
+        <is>
+          <t>Serve hot with imli chutney. Label gluten. Hold 20 minutes on a rack.</t>
+        </is>
+      </c>
+      <c r="C21" s="31" t="n"/>
+      <c r="D21" s="31" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="21" t="inlineStr">
+        <is>
+          <t>Nutrition per portion</t>
+        </is>
+      </c>
+      <c r="B23" s="22" t="n"/>
+      <c r="C23" s="22" t="n"/>
+      <c r="D23" s="22" t="n"/>
+    </row>
+    <row r="24" ht="36" customHeight="1">
+      <c r="A24" s="12" t="inlineStr">
+        <is>
+          <t>kcal 0  ·  Protein 0 g  ·  Carbs 0 g  ·  Fat 0 g  ·  Fibre 0 g. Nutrition is a kitchen estimate from typical produce values, not a laboratory analysis.</t>
+        </is>
+      </c>
+      <c r="B24" s="49" t="n"/>
+      <c r="C24" s="49" t="n"/>
+      <c r="D24" s="49" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="24" t="inlineStr">
+        <is>
+          <t>Allergens</t>
+        </is>
+      </c>
+      <c r="B25" s="6" t="n"/>
+      <c r="C25" s="6" t="n"/>
+      <c r="D25" s="6" t="n"/>
+    </row>
+    <row r="26" ht="48" customHeight="1">
+      <c r="A26" s="25" t="inlineStr">
+        <is>
+          <t>Gluten (wheat) · Milk · Always verify labels; this card is a kitchen estimate, not a lab certificate.</t>
+        </is>
+      </c>
+      <c r="B26" s="26" t="n"/>
+      <c r="C26" s="26" t="n"/>
+      <c r="D26" s="26" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="24" t="inlineStr">
+        <is>
+          <t>Chef notes</t>
+        </is>
+      </c>
+      <c r="B27" s="6" t="n"/>
+      <c r="C27" s="6" t="n"/>
+      <c r="D27" s="6" t="n"/>
+    </row>
+    <row r="28" ht="72" customHeight="1">
+      <c r="A28" s="25" t="inlineStr">
+        <is>
+          <t>For Samosa (nationwide aloo, no onion): keep the mix slightly drier than you think; wet mixes split or go greasy. Bloom hing in hot fat 20–30 seconds; raw hing tastes medicinal. Commercial hing is often cut with wheat flour — use a gluten-free hing if you must mark Gluten Free. Never cook tomato, tamarind, lemon, yogurt or milk in aluminium; use stainless steel, iron, clay or glass. Spice blends: read the packet. Many garam masalas hide onion or garlic powder.</t>
+        </is>
+      </c>
+      <c r="B28" s="26" t="n"/>
+      <c r="C28" s="26" t="n"/>
+      <c r="D28" s="26" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="50" t="inlineStr">
+        <is>
+          <t>Service notes</t>
+        </is>
+      </c>
+      <c r="B29" s="51" t="n"/>
+      <c r="C29" s="51" t="n"/>
+      <c r="D29" s="51" t="n"/>
+    </row>
+    <row r="30" ht="64" customHeight="1">
+      <c r="A30" s="12" t="inlineStr">
+        <is>
+          <t>Serve immediately while crisp or hot. Offer a chutney or raita that is also onion-garlic free. Service temperature: Hot. Allergen label for this dish: Gluten (wheat); Milk; Always verify labels; this card is a kitchen estimate, not a lab certificate. State clearly: vegetarian, no onion, no garlic, no eggs, no meat, no fish. Nutrition on this card is an estimate for 1 portion of 4.</t>
+        </is>
+      </c>
+      <c r="B30" s="49" t="n"/>
+      <c r="C30" s="49" t="n"/>
+      <c r="D30" s="49" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="23">
+    <mergeCell ref="A23:D23"/>
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="B17:D17"/>
+    <mergeCell ref="A29:D29"/>
+    <mergeCell ref="A28:D28"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="B19:D19"/>
+    <mergeCell ref="A30:D30"/>
+    <mergeCell ref="A24:D24"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B15:D15"/>
+    <mergeCell ref="B20:D20"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="C12:D12"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="A25:D25"/>
+    <mergeCell ref="B16:D16"/>
+    <mergeCell ref="A27:D27"/>
     <mergeCell ref="A3:D3"/>
+    <mergeCell ref="A26:D26"/>
+    <mergeCell ref="B18:D18"/>
+    <mergeCell ref="B21:D21"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="B15:D15"/>
-    <mergeCell ref="B16:D16"/>
     <mergeCell ref="A14:D14"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6002,7 +8284,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D16"/>
+  <dimension ref="A1:D29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -6014,7 +8296,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RECIPE CARD  ·  Pakora mixed veg (no onion)</t>
+          <t>Parslia Kitchen OS · RECIPE CARD · Pakora mixed veg (no onion)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6024,7 +8306,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Pan-India kitchen  ·  Starter  ·  Dishes cooked in homes all over India</t>
+          <t>Pure Prasad · No onion · No garlic · No eggs · No meat · No fish  ·  Pan-India  ·  Starter</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -6044,44 +8326,44 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="38" t="inlineStr">
         <is>
-          <t>Serves</t>
+          <t>YIELD</t>
         </is>
       </c>
       <c r="B5" s="38" t="inlineStr">
         <is>
-          <t>Prep</t>
+          <t>PORTION</t>
         </is>
       </c>
       <c r="C5" s="38" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>SERVICE</t>
         </is>
       </c>
       <c r="D5" s="38" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>TIME</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="39" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 portions</t>
         </is>
       </c>
       <c r="B6" s="39" t="inlineStr">
         <is>
-          <t>20 min</t>
+          <t>1 portion</t>
         </is>
       </c>
       <c r="C6" s="39" t="inlineStr">
         <is>
-          <t>20 min</t>
+          <t>Hot</t>
         </is>
       </c>
       <c r="D6" s="39" t="inlineStr">
         <is>
-          <t>40 min</t>
+          <t>Prep 20 min · Cook 20 min</t>
         </is>
       </c>
     </row>
@@ -6157,29 +8439,169 @@
       <c r="C15" s="45" t="n"/>
       <c r="D15" s="45" t="n"/>
     </row>
-    <row r="16" ht="36" customHeight="1">
+    <row r="16" ht="54" customHeight="1">
       <c r="A16" s="46" t="n">
         <v>1</v>
       </c>
       <c r="B16" s="47" t="inlineStr">
         <is>
-          <t>Dip. Fry. Chutney.</t>
+          <t>Mise en place. Slice potato, spinach and chilli; cube paneer. Whisk a thick besan batter with ajwain, hing, chilli and salt. Steel kadhai — never aluminium. No onion rings.</t>
         </is>
       </c>
       <c r="C16" s="48" t="n"/>
       <c r="D16" s="48" t="n"/>
     </row>
+    <row r="17" ht="54" customHeight="1">
+      <c r="A17" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="B17" s="30" t="inlineStr">
+        <is>
+          <t>Heat oil to 175–180 C. Dip pieces so they are coated, not drowning. Fry in batches 3–5 minutes until the crust is gold and the vegetable is tender.</t>
+        </is>
+      </c>
+      <c r="C17" s="31" t="n"/>
+      <c r="D17" s="31" t="n"/>
+    </row>
+    <row r="18" ht="42" customHeight="1">
+      <c r="A18" s="46" t="n">
+        <v>3</v>
+      </c>
+      <c r="B18" s="47" t="inlineStr">
+        <is>
+          <t>Do not crowd — temperature drop makes soggy pakora. Drain on a steel rack, not a heap of paper in the bowl.</t>
+        </is>
+      </c>
+      <c r="C18" s="48" t="n"/>
+      <c r="D18" s="48" t="n"/>
+    </row>
+    <row r="19" ht="42" customHeight="1">
+      <c r="A19" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="B19" s="30" t="inlineStr">
+        <is>
+          <t>Doneness: crisp shell, no raw besan, paneer hot. Serve at once with chutney.</t>
+        </is>
+      </c>
+      <c r="C19" s="31" t="n"/>
+      <c r="D19" s="31" t="n"/>
+    </row>
+    <row r="20" ht="42" customHeight="1">
+      <c r="A20" s="46" t="n">
+        <v>5</v>
+      </c>
+      <c r="B20" s="47" t="inlineStr">
+        <is>
+          <t>Hold 10 minutes only. Label gluten (besan is usually chickpea; still check hing) and milk if paneer is in the mix.</t>
+        </is>
+      </c>
+      <c r="C20" s="48" t="n"/>
+      <c r="D20" s="48" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="21" t="inlineStr">
+        <is>
+          <t>Nutrition per portion</t>
+        </is>
+      </c>
+      <c r="B22" s="22" t="n"/>
+      <c r="C22" s="22" t="n"/>
+      <c r="D22" s="22" t="n"/>
+    </row>
+    <row r="23" ht="36" customHeight="1">
+      <c r="A23" s="12" t="inlineStr">
+        <is>
+          <t>kcal 0  ·  Protein 0 g  ·  Carbs 0 g  ·  Fat 0 g  ·  Fibre 0 g. Nutrition is a kitchen estimate from typical produce values, not a laboratory analysis.</t>
+        </is>
+      </c>
+      <c r="B23" s="49" t="n"/>
+      <c r="C23" s="49" t="n"/>
+      <c r="D23" s="49" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="24" t="inlineStr">
+        <is>
+          <t>Allergens</t>
+        </is>
+      </c>
+      <c r="B24" s="6" t="n"/>
+      <c r="C24" s="6" t="n"/>
+      <c r="D24" s="6" t="n"/>
+    </row>
+    <row r="25" ht="48" customHeight="1">
+      <c r="A25" s="25" t="inlineStr">
+        <is>
+          <t>Gluten (wheat) · Milk · Always verify labels; this card is a kitchen estimate, not a lab certificate.</t>
+        </is>
+      </c>
+      <c r="B25" s="26" t="n"/>
+      <c r="C25" s="26" t="n"/>
+      <c r="D25" s="26" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="24" t="inlineStr">
+        <is>
+          <t>Chef notes</t>
+        </is>
+      </c>
+      <c r="B26" s="6" t="n"/>
+      <c r="C26" s="6" t="n"/>
+      <c r="D26" s="6" t="n"/>
+    </row>
+    <row r="27" ht="72" customHeight="1">
+      <c r="A27" s="25" t="inlineStr">
+        <is>
+          <t>For Pakora mixed veg (no onion): keep the mix slightly drier than you think; wet mixes split or go greasy. Bloom hing in hot fat 20–30 seconds; raw hing tastes medicinal. Commercial hing is often cut with wheat flour — use a gluten-free hing if you must mark Gluten Free. Never cook tomato, tamarind, lemon, yogurt or milk in aluminium; use stainless steel, iron, clay or glass. Spice blends: read the packet. Many garam masalas hide onion or garlic powder.</t>
+        </is>
+      </c>
+      <c r="B27" s="26" t="n"/>
+      <c r="C27" s="26" t="n"/>
+      <c r="D27" s="26" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="50" t="inlineStr">
+        <is>
+          <t>Service notes</t>
+        </is>
+      </c>
+      <c r="B28" s="51" t="n"/>
+      <c r="C28" s="51" t="n"/>
+      <c r="D28" s="51" t="n"/>
+    </row>
+    <row r="29" ht="64" customHeight="1">
+      <c r="A29" s="12" t="inlineStr">
+        <is>
+          <t>Serve immediately while crisp or hot. Offer a chutney or raita that is also onion-garlic free. Service temperature: Hot. Allergen label for this dish: Gluten (wheat); Milk; Always verify labels; this card is a kitchen estimate, not a lab certificate. State clearly: vegetarian, no onion, no garlic, no eggs, no meat, no fish. Nutrition on this card is an estimate for 1 portion of 4.</t>
+        </is>
+      </c>
+      <c r="B29" s="49" t="n"/>
+      <c r="C29" s="49" t="n"/>
+      <c r="D29" s="49" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="22">
+    <mergeCell ref="A23:D23"/>
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="A22:D22"/>
+    <mergeCell ref="B17:D17"/>
+    <mergeCell ref="A29:D29"/>
+    <mergeCell ref="A28:D28"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="B19:D19"/>
+    <mergeCell ref="A24:D24"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B15:D15"/>
+    <mergeCell ref="B20:D20"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="C12:D12"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="A25:D25"/>
+    <mergeCell ref="B16:D16"/>
+    <mergeCell ref="A27:D27"/>
     <mergeCell ref="A3:D3"/>
+    <mergeCell ref="A26:D26"/>
+    <mergeCell ref="B18:D18"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="B15:D15"/>
-    <mergeCell ref="B16:D16"/>
     <mergeCell ref="A14:D14"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6194,7 +8616,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D18"/>
+  <dimension ref="A1:D33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -6206,7 +8628,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RECIPE CARD  ·  Idli sambar plate (South + national, no onion garlic sambar)</t>
+          <t>Parslia Kitchen OS · RECIPE CARD · Idli sambar plate (South + national, no onion garlic sambar)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6216,7 +8638,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Pan-India kitchen  ·  Starter  ·  Dishes cooked in homes all over India</t>
+          <t>Pure Prasad · No onion · No garlic · No eggs · No meat · No fish  ·  Pan-India  ·  Starter</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -6236,44 +8658,44 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="38" t="inlineStr">
         <is>
-          <t>Serves</t>
+          <t>YIELD</t>
         </is>
       </c>
       <c r="B5" s="38" t="inlineStr">
         <is>
-          <t>Prep</t>
+          <t>PORTION</t>
         </is>
       </c>
       <c r="C5" s="38" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>SERVICE</t>
         </is>
       </c>
       <c r="D5" s="38" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>TIME</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="39" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 portions</t>
         </is>
       </c>
       <c r="B6" s="39" t="inlineStr">
         <is>
-          <t>20 min</t>
+          <t>1 portion</t>
         </is>
       </c>
       <c r="C6" s="39" t="inlineStr">
         <is>
-          <t>25 min</t>
+          <t>Hot</t>
         </is>
       </c>
       <c r="D6" s="39" t="inlineStr">
         <is>
-          <t>45 min</t>
+          <t>Prep 20 min · Cook 25 min</t>
         </is>
       </c>
     </row>
@@ -6385,32 +8807,198 @@
       <c r="C17" s="45" t="n"/>
       <c r="D17" s="45" t="n"/>
     </row>
-    <row r="18" ht="36" customHeight="1">
+    <row r="18" ht="66" customHeight="1">
       <c r="A18" s="46" t="n">
         <v>1</v>
       </c>
       <c r="B18" s="47" t="inlineStr">
         <is>
-          <t>Steam idli. Cook sambar in kadai. Coconut chutney ginger-chilli.</t>
+          <t>Mise en place. Idli batter ready. For sambar: toor dal, pumpkin, drumstick, tomato, tamarind, sambar powder with no onion or garlic, mustard, hing, curry leaf. Stainless steel steamer and kadhai — never aluminium.</t>
         </is>
       </c>
       <c r="C18" s="48" t="n"/>
       <c r="D18" s="48" t="n"/>
     </row>
+    <row r="19" ht="42" customHeight="1">
+      <c r="A19" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="B19" s="30" t="inlineStr">
+        <is>
+          <t>Steam idlis in a greased steel mould 10–12 minutes until a wet finger does not stick. Rest 1 minute before unmoulding.</t>
+        </is>
+      </c>
+      <c r="C19" s="31" t="n"/>
+      <c r="D19" s="31" t="n"/>
+    </row>
+    <row r="20" ht="42" customHeight="1">
+      <c r="A20" s="46" t="n">
+        <v>3</v>
+      </c>
+      <c r="B20" s="47" t="inlineStr">
+        <is>
+          <t>Cook dal and vegetables until soft. Add tamarind and sambar powder. Simmer 8 minutes.</t>
+        </is>
+      </c>
+      <c r="C20" s="48" t="n"/>
+      <c r="D20" s="48" t="n"/>
+    </row>
+    <row r="21" ht="42" customHeight="1">
+      <c r="A21" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="B21" s="30" t="inlineStr">
+        <is>
+          <t>Tadka: mustard, hing, curry leaf in ghee 20–30 seconds. Pour over. No onion, no garlic, no sambar onion paste.</t>
+        </is>
+      </c>
+      <c r="C21" s="31" t="n"/>
+      <c r="D21" s="31" t="n"/>
+    </row>
+    <row r="22" ht="42" customHeight="1">
+      <c r="A22" s="46" t="n">
+        <v>5</v>
+      </c>
+      <c r="B22" s="47" t="inlineStr">
+        <is>
+          <t>Coconut chutney: coconut, ginger, chilli, salt, tempered mustard — no onion.</t>
+        </is>
+      </c>
+      <c r="C22" s="48" t="n"/>
+      <c r="D22" s="48" t="n"/>
+    </row>
+    <row r="23" ht="42" customHeight="1">
+      <c r="A23" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="B23" s="30" t="inlineStr">
+        <is>
+          <t>Doneness: idli spongy; sambar coats a spoon, not watery. Serve hot, 3 idlis per portion with a ladle of sambar.</t>
+        </is>
+      </c>
+      <c r="C23" s="31" t="n"/>
+      <c r="D23" s="31" t="n"/>
+    </row>
+    <row r="24" ht="42" customHeight="1">
+      <c r="A24" s="46" t="n">
+        <v>7</v>
+      </c>
+      <c r="B24" s="47" t="inlineStr">
+        <is>
+          <t>Hold idlis in a covered steamer off the boil. Hold sambar hot. Label coconut and possible gluten in hing.</t>
+        </is>
+      </c>
+      <c r="C24" s="48" t="n"/>
+      <c r="D24" s="48" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="21" t="inlineStr">
+        <is>
+          <t>Nutrition per portion</t>
+        </is>
+      </c>
+      <c r="B26" s="22" t="n"/>
+      <c r="C26" s="22" t="n"/>
+      <c r="D26" s="22" t="n"/>
+    </row>
+    <row r="27" ht="36" customHeight="1">
+      <c r="A27" s="12" t="inlineStr">
+        <is>
+          <t>kcal 279  ·  Protein 13 g  ·  Carbs 46 g  ·  Fat 6 g  ·  Fibre 9 g. Nutrition is a kitchen estimate from typical produce values, not a laboratory analysis.</t>
+        </is>
+      </c>
+      <c r="B27" s="49" t="n"/>
+      <c r="C27" s="49" t="n"/>
+      <c r="D27" s="49" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="24" t="inlineStr">
+        <is>
+          <t>Allergens</t>
+        </is>
+      </c>
+      <c r="B28" s="6" t="n"/>
+      <c r="C28" s="6" t="n"/>
+      <c r="D28" s="6" t="n"/>
+    </row>
+    <row r="29" ht="48" customHeight="1">
+      <c r="A29" s="25" t="inlineStr">
+        <is>
+          <t>Gluten (wheat) · Milk · Mustard · Always verify labels; this card is a kitchen estimate, not a lab certificate.</t>
+        </is>
+      </c>
+      <c r="B29" s="26" t="n"/>
+      <c r="C29" s="26" t="n"/>
+      <c r="D29" s="26" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="24" t="inlineStr">
+        <is>
+          <t>Chef notes</t>
+        </is>
+      </c>
+      <c r="B30" s="6" t="n"/>
+      <c r="C30" s="6" t="n"/>
+      <c r="D30" s="6" t="n"/>
+    </row>
+    <row r="31" ht="72" customHeight="1">
+      <c r="A31" s="25" t="inlineStr">
+        <is>
+          <t>For Idli sambar plate (South + national, no onion garlic sambar): keep the mix slightly drier than you think; wet mixes split or go greasy. Bloom hing in hot fat 20–30 seconds; raw hing tastes medicinal. Commercial hing is often cut with wheat flour — use a gluten-free hing if you must mark Gluten Free. Never cook tomato, tamarind, lemon, yogurt or milk in aluminium; use stainless steel, iron, clay or glass. Spice blends: read the packet. Many garam masalas hide onion or garlic powder.</t>
+        </is>
+      </c>
+      <c r="B31" s="26" t="n"/>
+      <c r="C31" s="26" t="n"/>
+      <c r="D31" s="26" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="50" t="inlineStr">
+        <is>
+          <t>Service notes</t>
+        </is>
+      </c>
+      <c r="B32" s="51" t="n"/>
+      <c r="C32" s="51" t="n"/>
+      <c r="D32" s="51" t="n"/>
+    </row>
+    <row r="33" ht="64" customHeight="1">
+      <c r="A33" s="12" t="inlineStr">
+        <is>
+          <t>Serve immediately while crisp or hot. Offer a chutney or raita that is also onion-garlic free. Service temperature: Hot. Allergen label for this dish: Gluten (wheat); Milk; Mustard; Always verify labels; this card is a kitchen estimate, not a lab certificate. State clearly: vegetarian, no onion, no garlic, no eggs, no meat, no fish. Nutrition on this card is an estimate for 1 portion of 4.</t>
+        </is>
+      </c>
+      <c r="B33" s="49" t="n"/>
+      <c r="C33" s="49" t="n"/>
+      <c r="D33" s="49" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="12">
+  <mergeCells count="26">
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="B17:D17"/>
+    <mergeCell ref="A29:D29"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="A28:D28"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="B19:D19"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="A30:D30"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="B20:D20"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="C12:D12"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="A16:D16"/>
+    <mergeCell ref="A27:D27"/>
+    <mergeCell ref="B22:D22"/>
     <mergeCell ref="A3:D3"/>
-    <mergeCell ref="B17:D17"/>
+    <mergeCell ref="A26:D26"/>
     <mergeCell ref="B18:D18"/>
-    <mergeCell ref="C14:D14"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="A16:D16"/>
+    <mergeCell ref="B21:D21"/>
+    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="A32:D32"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -6424,7 +9012,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D17"/>
+  <dimension ref="A1:D31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -6436,7 +9024,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RECIPE CARD  ·  Dal tadka (yellow dal, no onion garlic)</t>
+          <t>Parslia Kitchen OS · RECIPE CARD · Dal tadka (yellow dal, no onion garlic)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6446,7 +9034,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Pan-India kitchen  ·  Main  ·  Dishes cooked in homes all over India</t>
+          <t>Pure Prasad · No onion · No garlic · No eggs · No meat · No fish  ·  Pan-India  ·  Main</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -6466,44 +9054,44 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="38" t="inlineStr">
         <is>
-          <t>Serves</t>
+          <t>YIELD</t>
         </is>
       </c>
       <c r="B5" s="38" t="inlineStr">
         <is>
-          <t>Prep</t>
+          <t>PORTION</t>
         </is>
       </c>
       <c r="C5" s="38" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>SERVICE</t>
         </is>
       </c>
       <c r="D5" s="38" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>TIME</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="39" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 portions</t>
         </is>
       </c>
       <c r="B6" s="39" t="inlineStr">
         <is>
-          <t>10 min</t>
+          <t>1 portion</t>
         </is>
       </c>
       <c r="C6" s="39" t="inlineStr">
         <is>
-          <t>30 min</t>
+          <t>Hot</t>
         </is>
       </c>
       <c r="D6" s="39" t="inlineStr">
         <is>
-          <t>40 min</t>
+          <t>Prep 10 min · Cook 30 min</t>
         </is>
       </c>
     </row>
@@ -6597,31 +9185,184 @@
       <c r="C16" s="45" t="n"/>
       <c r="D16" s="45" t="n"/>
     </row>
-    <row r="17" ht="36" customHeight="1">
+    <row r="17" ht="42" customHeight="1">
       <c r="A17" s="46" t="n">
         <v>1</v>
       </c>
       <c r="B17" s="47" t="inlineStr">
         <is>
-          <t>Boil dal. Temper. National restaurant sattvic version.</t>
+          <t>Mise en place. Wash 1.5 cups toor dal. Set a steel pot and a tadka pan — never aluminium. No fried onion.</t>
         </is>
       </c>
       <c r="C17" s="48" t="n"/>
       <c r="D17" s="48" t="n"/>
     </row>
+    <row r="18" ht="42" customHeight="1">
+      <c r="A18" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="B18" s="30" t="inlineStr">
+        <is>
+          <t>Cook dal with turmeric and water until completely soft, 20–25 minutes. Mash lightly. Add chopped tomato and salt. Simmer 5 minutes.</t>
+        </is>
+      </c>
+      <c r="C18" s="31" t="n"/>
+      <c r="D18" s="31" t="n"/>
+    </row>
+    <row r="19" ht="42" customHeight="1">
+      <c r="A19" s="46" t="n">
+        <v>3</v>
+      </c>
+      <c r="B19" s="47" t="inlineStr">
+        <is>
+          <t>Tadka: ghee, cumin, hing, dry chilli — bloom 20–30 seconds until fragrant. Pour over the dal. Cover 1 minute.</t>
+        </is>
+      </c>
+      <c r="C19" s="48" t="n"/>
+      <c r="D19" s="48" t="n"/>
+    </row>
+    <row r="20" ht="36" customHeight="1">
+      <c r="A20" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="B20" s="30" t="inlineStr">
+        <is>
+          <t>Finish coriander. Consistency should be pourable, not paste.</t>
+        </is>
+      </c>
+      <c r="C20" s="31" t="n"/>
+      <c r="D20" s="31" t="n"/>
+    </row>
+    <row r="21" ht="42" customHeight="1">
+      <c r="A21" s="46" t="n">
+        <v>5</v>
+      </c>
+      <c r="B21" s="47" t="inlineStr">
+        <is>
+          <t>Doneness: no whole grains of dal, tadka aroma on top. Serve hot with rice or roti.</t>
+        </is>
+      </c>
+      <c r="C21" s="48" t="n"/>
+      <c r="D21" s="48" t="n"/>
+    </row>
+    <row r="22" ht="42" customHeight="1">
+      <c r="A22" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="B22" s="30" t="inlineStr">
+        <is>
+          <t>Hold hot, stirred. Loosen with hot water as it sits. Label possible gluten in hing.</t>
+        </is>
+      </c>
+      <c r="C22" s="31" t="n"/>
+      <c r="D22" s="31" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="21" t="inlineStr">
+        <is>
+          <t>Nutrition per portion</t>
+        </is>
+      </c>
+      <c r="B24" s="22" t="n"/>
+      <c r="C24" s="22" t="n"/>
+      <c r="D24" s="22" t="n"/>
+    </row>
+    <row r="25" ht="36" customHeight="1">
+      <c r="A25" s="12" t="inlineStr">
+        <is>
+          <t>kcal 193  ·  Protein 12 g  ·  Carbs 35 g  ·  Fat 1 g  ·  Fibre 8 g. Nutrition is a kitchen estimate from typical produce values, not a laboratory analysis.</t>
+        </is>
+      </c>
+      <c r="B25" s="49" t="n"/>
+      <c r="C25" s="49" t="n"/>
+      <c r="D25" s="49" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="24" t="inlineStr">
+        <is>
+          <t>Allergens</t>
+        </is>
+      </c>
+      <c r="B26" s="6" t="n"/>
+      <c r="C26" s="6" t="n"/>
+      <c r="D26" s="6" t="n"/>
+    </row>
+    <row r="27" ht="48" customHeight="1">
+      <c r="A27" s="25" t="inlineStr">
+        <is>
+          <t>Gluten (wheat) · Milk · Always verify labels; this card is a kitchen estimate, not a lab certificate.</t>
+        </is>
+      </c>
+      <c r="B27" s="26" t="n"/>
+      <c r="C27" s="26" t="n"/>
+      <c r="D27" s="26" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="24" t="inlineStr">
+        <is>
+          <t>Chef notes</t>
+        </is>
+      </c>
+      <c r="B28" s="6" t="n"/>
+      <c r="C28" s="6" t="n"/>
+      <c r="D28" s="6" t="n"/>
+    </row>
+    <row r="29" ht="72" customHeight="1">
+      <c r="A29" s="25" t="inlineStr">
+        <is>
+          <t>For Dal tadka (yellow dal, no onion garlic): keep the mix slightly drier than you think; wet mixes split or go greasy. Bloom hing in hot fat 20–30 seconds; raw hing tastes medicinal. Commercial hing is often cut with wheat flour — use a gluten-free hing if you must mark Gluten Free. Never cook tomato, tamarind, lemon, yogurt or milk in aluminium; use stainless steel, iron, clay or glass. Spice blends: read the packet. Many garam masalas hide onion or garlic powder.</t>
+        </is>
+      </c>
+      <c r="B29" s="26" t="n"/>
+      <c r="C29" s="26" t="n"/>
+      <c r="D29" s="26" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="50" t="inlineStr">
+        <is>
+          <t>Service notes</t>
+        </is>
+      </c>
+      <c r="B30" s="51" t="n"/>
+      <c r="C30" s="51" t="n"/>
+      <c r="D30" s="51" t="n"/>
+    </row>
+    <row r="31" ht="64" customHeight="1">
+      <c r="A31" s="12" t="inlineStr">
+        <is>
+          <t>Plate with bread or rice from the same kitchen card. Sauce should nap, not flood. Service temperature: Hot. Allergen label for this dish: Gluten (wheat); Milk; Always verify labels; this card is a kitchen estimate, not a lab certificate. State clearly: vegetarian, no onion, no garlic, no eggs, no meat, no fish. Nutrition on this card is an estimate for 1 portion of 4.</t>
+        </is>
+      </c>
+      <c r="B31" s="49" t="n"/>
+      <c r="C31" s="49" t="n"/>
+      <c r="D31" s="49" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="11">
+  <mergeCells count="24">
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="B17:D17"/>
+    <mergeCell ref="A29:D29"/>
+    <mergeCell ref="A28:D28"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="B19:D19"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="A30:D30"/>
+    <mergeCell ref="A15:D15"/>
+    <mergeCell ref="A24:D24"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B20:D20"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="C12:D12"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="A25:D25"/>
+    <mergeCell ref="B16:D16"/>
+    <mergeCell ref="A27:D27"/>
+    <mergeCell ref="B22:D22"/>
     <mergeCell ref="A3:D3"/>
-    <mergeCell ref="B17:D17"/>
-    <mergeCell ref="A15:D15"/>
+    <mergeCell ref="A26:D26"/>
+    <mergeCell ref="B18:D18"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="B16:D16"/>
+    <mergeCell ref="B21:D21"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -6635,7 +9376,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D19"/>
+  <dimension ref="A1:D33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -6647,7 +9388,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RECIPE CARD  ·  Palak paneer (no onion garlic)</t>
+          <t>Parslia Kitchen OS · RECIPE CARD · Palak paneer (no onion garlic)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6657,7 +9398,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Pan-India kitchen  ·  Main  ·  Dishes cooked in homes all over India</t>
+          <t>Pure Prasad · No onion · No garlic · No eggs · No meat · No fish  ·  Pan-India  ·  Main</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -6677,44 +9418,44 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="38" t="inlineStr">
         <is>
-          <t>Serves</t>
+          <t>YIELD</t>
         </is>
       </c>
       <c r="B5" s="38" t="inlineStr">
         <is>
-          <t>Prep</t>
+          <t>PORTION</t>
         </is>
       </c>
       <c r="C5" s="38" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>SERVICE</t>
         </is>
       </c>
       <c r="D5" s="38" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>TIME</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="39" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 portions</t>
         </is>
       </c>
       <c r="B6" s="39" t="inlineStr">
         <is>
-          <t>20 min</t>
+          <t>1 portion</t>
         </is>
       </c>
       <c r="C6" s="39" t="inlineStr">
         <is>
-          <t>25 min</t>
+          <t>Hot</t>
         </is>
       </c>
       <c r="D6" s="39" t="inlineStr">
         <is>
-          <t>45 min</t>
+          <t>Prep 20 min · Cook 25 min</t>
         </is>
       </c>
     </row>
@@ -6844,33 +9585,186 @@
       <c r="C18" s="45" t="n"/>
       <c r="D18" s="45" t="n"/>
     </row>
-    <row r="19" ht="36" customHeight="1">
+    <row r="19" ht="42" customHeight="1">
       <c r="A19" s="46" t="n">
         <v>1</v>
       </c>
       <c r="B19" s="47" t="inlineStr">
         <is>
-          <t>Blanch spinach. Puree. Cook masala. Add puree and paneer.</t>
+          <t>Mise en place. Wash 500 g spinach. Cube 300 g paneer. Set a steel pot and kadhai — never aluminium. No onion paste.</t>
         </is>
       </c>
       <c r="C19" s="48" t="n"/>
       <c r="D19" s="48" t="n"/>
     </row>
+    <row r="20" ht="42" customHeight="1">
+      <c r="A20" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="B20" s="30" t="inlineStr">
+        <is>
+          <t>Blanch spinach 45–60 seconds. Shock. Squeeze dry. Puree with ginger and green chilli, leaving a little texture.</t>
+        </is>
+      </c>
+      <c r="C20" s="31" t="n"/>
+      <c r="D20" s="31" t="n"/>
+    </row>
+    <row r="21" ht="54" customHeight="1">
+      <c r="A21" s="46" t="n">
+        <v>3</v>
+      </c>
+      <c r="B21" s="47" t="inlineStr">
+        <is>
+          <t>Heat ghee. Bloom cumin and hing 20–30 seconds. Cook chopped tomato 5–6 minutes. Add puree. Simmer 6–8 minutes until the raw spinach smell goes.</t>
+        </is>
+      </c>
+      <c r="C21" s="48" t="n"/>
+      <c r="D21" s="48" t="n"/>
+    </row>
+    <row r="22" ht="42" customHeight="1">
+      <c r="A22" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="B22" s="30" t="inlineStr">
+        <is>
+          <t>Add paneer, garam masala, salt and optional cream. Simmer 3 minutes only — longer and the paneer toughens.</t>
+        </is>
+      </c>
+      <c r="C22" s="31" t="n"/>
+      <c r="D22" s="31" t="n"/>
+    </row>
+    <row r="23" ht="42" customHeight="1">
+      <c r="A23" s="46" t="n">
+        <v>5</v>
+      </c>
+      <c r="B23" s="47" t="inlineStr">
+        <is>
+          <t>Doneness: gravy coats paneer, colour deep green, no watery pool. Serve hot.</t>
+        </is>
+      </c>
+      <c r="C23" s="48" t="n"/>
+      <c r="D23" s="48" t="n"/>
+    </row>
+    <row r="24" ht="36" customHeight="1">
+      <c r="A24" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="B24" s="30" t="inlineStr">
+        <is>
+          <t>Hold hot up to 20 minutes. Label milk. Do not reboil hard.</t>
+        </is>
+      </c>
+      <c r="C24" s="31" t="n"/>
+      <c r="D24" s="31" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="21" t="inlineStr">
+        <is>
+          <t>Nutrition per portion</t>
+        </is>
+      </c>
+      <c r="B26" s="22" t="n"/>
+      <c r="C26" s="22" t="n"/>
+      <c r="D26" s="22" t="n"/>
+    </row>
+    <row r="27" ht="36" customHeight="1">
+      <c r="A27" s="12" t="inlineStr">
+        <is>
+          <t>kcal 232  ·  Protein 17 g  ·  Carbs 7 g  ·  Fat 16 g  ·  Fibre 3 g. Nutrition is a kitchen estimate from typical produce values, not a laboratory analysis.</t>
+        </is>
+      </c>
+      <c r="B27" s="49" t="n"/>
+      <c r="C27" s="49" t="n"/>
+      <c r="D27" s="49" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="24" t="inlineStr">
+        <is>
+          <t>Allergens</t>
+        </is>
+      </c>
+      <c r="B28" s="6" t="n"/>
+      <c r="C28" s="6" t="n"/>
+      <c r="D28" s="6" t="n"/>
+    </row>
+    <row r="29" ht="48" customHeight="1">
+      <c r="A29" s="25" t="inlineStr">
+        <is>
+          <t>Gluten (wheat) · Milk · Always verify labels; this card is a kitchen estimate, not a lab certificate.</t>
+        </is>
+      </c>
+      <c r="B29" s="26" t="n"/>
+      <c r="C29" s="26" t="n"/>
+      <c r="D29" s="26" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="24" t="inlineStr">
+        <is>
+          <t>Chef notes</t>
+        </is>
+      </c>
+      <c r="B30" s="6" t="n"/>
+      <c r="C30" s="6" t="n"/>
+      <c r="D30" s="6" t="n"/>
+    </row>
+    <row r="31" ht="72" customHeight="1">
+      <c r="A31" s="25" t="inlineStr">
+        <is>
+          <t>Wash greens until the water is clear; grit ruins the dish. For Palak paneer (no onion garlic): keep the mix slightly drier than you think; wet mixes split or go greasy. Bloom hing in hot fat 20–30 seconds; raw hing tastes medicinal. Commercial hing is often cut with wheat flour — use a gluten-free hing if you must mark Gluten Free. Never cook tomato, tamarind, lemon, yogurt or milk in aluminium; use stainless steel, iron, clay or glass. Spice blends: read the packet. Many garam masalas hide onion or garlic powder. Pat paneer dry and do not boil it hard or it turns rubbery.</t>
+        </is>
+      </c>
+      <c r="B31" s="26" t="n"/>
+      <c r="C31" s="26" t="n"/>
+      <c r="D31" s="26" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="50" t="inlineStr">
+        <is>
+          <t>Service notes</t>
+        </is>
+      </c>
+      <c r="B32" s="51" t="n"/>
+      <c r="C32" s="51" t="n"/>
+      <c r="D32" s="51" t="n"/>
+    </row>
+    <row r="33" ht="64" customHeight="1">
+      <c r="A33" s="12" t="inlineStr">
+        <is>
+          <t>Plate with bread or rice from the same kitchen card. Sauce should nap, not flood. Service temperature: Hot. Allergen label for this dish: Gluten (wheat); Milk; Always verify labels; this card is a kitchen estimate, not a lab certificate. State clearly: vegetarian, no onion, no garlic, no eggs, no meat, no fish. Nutrition on this card is an estimate for 1 portion of 4.</t>
+        </is>
+      </c>
+      <c r="B33" s="49" t="n"/>
+      <c r="C33" s="49" t="n"/>
+      <c r="D33" s="49" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="13">
+  <mergeCells count="26">
+    <mergeCell ref="A17:D17"/>
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="A29:D29"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="A28:D28"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="B19:D19"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="A30:D30"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="B20:D20"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="C12:D12"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="A17:D17"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="B19:D19"/>
-    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="A27:D27"/>
+    <mergeCell ref="B22:D22"/>
     <mergeCell ref="A3:D3"/>
+    <mergeCell ref="A26:D26"/>
     <mergeCell ref="B18:D18"/>
-    <mergeCell ref="C14:D14"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B21:D21"/>
+    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="A32:D32"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -6884,7 +9778,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D17"/>
+  <dimension ref="A1:D30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -6896,7 +9790,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RECIPE CARD  ·  Chana masala (no onion garlic)</t>
+          <t>Parslia Kitchen OS · RECIPE CARD · Chana masala (no onion garlic)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6906,7 +9800,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Pan-India kitchen  ·  Main  ·  Dishes cooked in homes all over India</t>
+          <t>Pure Prasad · No onion · No garlic · No eggs · No meat · No fish  ·  Pan-India  ·  Main</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -6926,44 +9820,44 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="38" t="inlineStr">
         <is>
-          <t>Serves</t>
+          <t>YIELD</t>
         </is>
       </c>
       <c r="B5" s="38" t="inlineStr">
         <is>
-          <t>Prep</t>
+          <t>PORTION</t>
         </is>
       </c>
       <c r="C5" s="38" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>SERVICE</t>
         </is>
       </c>
       <c r="D5" s="38" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>TIME</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="39" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 portions</t>
         </is>
       </c>
       <c r="B6" s="39" t="inlineStr">
         <is>
-          <t>15 min</t>
+          <t>1 portion</t>
         </is>
       </c>
       <c r="C6" s="39" t="inlineStr">
         <is>
-          <t>40 min</t>
+          <t>Hot</t>
         </is>
       </c>
       <c r="D6" s="39" t="inlineStr">
         <is>
-          <t>55 min</t>
+          <t>Prep 15 min · Cook 40 min</t>
         </is>
       </c>
     </row>
@@ -7057,31 +9951,171 @@
       <c r="C16" s="45" t="n"/>
       <c r="D16" s="45" t="n"/>
     </row>
-    <row r="17" ht="36" customHeight="1">
+    <row r="17" ht="42" customHeight="1">
       <c r="A17" s="46" t="n">
         <v>1</v>
       </c>
       <c r="B17" s="47" t="inlineStr">
         <is>
-          <t>Cook chana in tomato-spice gravy.</t>
+          <t>Mise en place. Soak and cook 2 cups chickpeas until soft. Steel kadhai — never aluminium. Check masala packets for onion or garlic powder.</t>
         </is>
       </c>
       <c r="C17" s="48" t="n"/>
       <c r="D17" s="48" t="n"/>
     </row>
+    <row r="18" ht="42" customHeight="1">
+      <c r="A18" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="B18" s="30" t="inlineStr">
+        <is>
+          <t>Heat ghee. Bloom cumin and hing. Cook tomato with coriander, chilli, amchur, garam masala and salt until fat separates.</t>
+        </is>
+      </c>
+      <c r="C18" s="31" t="n"/>
+      <c r="D18" s="31" t="n"/>
+    </row>
+    <row r="19" ht="42" customHeight="1">
+      <c r="A19" s="46" t="n">
+        <v>3</v>
+      </c>
+      <c r="B19" s="47" t="inlineStr">
+        <is>
+          <t>Add chickpeas and a ladle of cooking liquor. Simmer 12–15 minutes, crushing a few chana for body.</t>
+        </is>
+      </c>
+      <c r="C19" s="48" t="n"/>
+      <c r="D19" s="48" t="n"/>
+    </row>
+    <row r="20" ht="36" customHeight="1">
+      <c r="A20" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="B20" s="30" t="inlineStr">
+        <is>
+          <t>Doneness: gravy thick, chickpeas creamy. Serve hot with roti or rice.</t>
+        </is>
+      </c>
+      <c r="C20" s="31" t="n"/>
+      <c r="D20" s="31" t="n"/>
+    </row>
+    <row r="21" ht="36" customHeight="1">
+      <c r="A21" s="46" t="n">
+        <v>5</v>
+      </c>
+      <c r="B21" s="47" t="inlineStr">
+        <is>
+          <t>Hold hot. Label legumes.</t>
+        </is>
+      </c>
+      <c r="C21" s="48" t="n"/>
+      <c r="D21" s="48" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="21" t="inlineStr">
+        <is>
+          <t>Nutrition per portion</t>
+        </is>
+      </c>
+      <c r="B23" s="22" t="n"/>
+      <c r="C23" s="22" t="n"/>
+      <c r="D23" s="22" t="n"/>
+    </row>
+    <row r="24" ht="36" customHeight="1">
+      <c r="A24" s="12" t="inlineStr">
+        <is>
+          <t>kcal 270  ·  Protein 14 g  ·  Carbs 46 g  ·  Fat 4 g  ·  Fibre 13 g. Nutrition is a kitchen estimate from typical produce values, not a laboratory analysis.</t>
+        </is>
+      </c>
+      <c r="B24" s="49" t="n"/>
+      <c r="C24" s="49" t="n"/>
+      <c r="D24" s="49" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="24" t="inlineStr">
+        <is>
+          <t>Allergens</t>
+        </is>
+      </c>
+      <c r="B25" s="6" t="n"/>
+      <c r="C25" s="6" t="n"/>
+      <c r="D25" s="6" t="n"/>
+    </row>
+    <row r="26" ht="48" customHeight="1">
+      <c r="A26" s="25" t="inlineStr">
+        <is>
+          <t>Gluten (wheat) · Milk · Always verify labels; this card is a kitchen estimate, not a lab certificate.</t>
+        </is>
+      </c>
+      <c r="B26" s="26" t="n"/>
+      <c r="C26" s="26" t="n"/>
+      <c r="D26" s="26" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="24" t="inlineStr">
+        <is>
+          <t>Chef notes</t>
+        </is>
+      </c>
+      <c r="B27" s="6" t="n"/>
+      <c r="C27" s="6" t="n"/>
+      <c r="D27" s="6" t="n"/>
+    </row>
+    <row r="28" ht="72" customHeight="1">
+      <c r="A28" s="25" t="inlineStr">
+        <is>
+          <t>For Chana masala (no onion garlic): keep the mix slightly drier than you think; wet mixes split or go greasy. Bloom hing in hot fat 20–30 seconds; raw hing tastes medicinal. Commercial hing is often cut with wheat flour — use a gluten-free hing if you must mark Gluten Free. Never cook tomato, tamarind, lemon, yogurt or milk in aluminium; use stainless steel, iron, clay or glass. Spice blends: read the packet. Many garam masalas hide onion or garlic powder.</t>
+        </is>
+      </c>
+      <c r="B28" s="26" t="n"/>
+      <c r="C28" s="26" t="n"/>
+      <c r="D28" s="26" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="50" t="inlineStr">
+        <is>
+          <t>Service notes</t>
+        </is>
+      </c>
+      <c r="B29" s="51" t="n"/>
+      <c r="C29" s="51" t="n"/>
+      <c r="D29" s="51" t="n"/>
+    </row>
+    <row r="30" ht="64" customHeight="1">
+      <c r="A30" s="12" t="inlineStr">
+        <is>
+          <t>Plate with bread or rice from the same kitchen card. Sauce should nap, not flood. Service temperature: Hot. Allergen label for this dish: Gluten (wheat); Milk; Always verify labels; this card is a kitchen estimate, not a lab certificate. State clearly: vegetarian, no onion, no garlic, no eggs, no meat, no fish. Nutrition on this card is an estimate for 1 portion of 4.</t>
+        </is>
+      </c>
+      <c r="B30" s="49" t="n"/>
+      <c r="C30" s="49" t="n"/>
+      <c r="D30" s="49" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="11">
+  <mergeCells count="23">
+    <mergeCell ref="A23:D23"/>
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="B17:D17"/>
+    <mergeCell ref="A29:D29"/>
+    <mergeCell ref="A28:D28"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="B19:D19"/>
+    <mergeCell ref="A30:D30"/>
+    <mergeCell ref="A15:D15"/>
+    <mergeCell ref="A24:D24"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B20:D20"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="C12:D12"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="A25:D25"/>
+    <mergeCell ref="B16:D16"/>
+    <mergeCell ref="A27:D27"/>
     <mergeCell ref="A3:D3"/>
-    <mergeCell ref="B17:D17"/>
-    <mergeCell ref="A15:D15"/>
+    <mergeCell ref="A26:D26"/>
+    <mergeCell ref="B18:D18"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="B16:D16"/>
+    <mergeCell ref="B21:D21"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
